--- a/docs/xlsx/jobs-2026-08-31.xlsx
+++ b/docs/xlsx/jobs-2026-08-31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="585">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1744 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>Kansas Department of Wildlife and Parks</t>
+  </si>
+  <si>
+    <t>Topeka, KS</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$23.75 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-accountant-topeka-kansas/2495880112</t>
+  </si>
+  <si>
+    <t>AmeriCorps Individual Placement – Fire Management Technician</t>
+  </si>
+  <si>
+    <t>Southeast Conservation Corps</t>
+  </si>
+  <si>
+    <t>Rome, GA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$550 per week</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-individual-placement--fire-management-technician-rome-georgia/2663534843</t>
+  </si>
+  <si>
+    <t>AmeriCorps Individual Placement – Natural Resource Technician</t>
+  </si>
+  <si>
+    <t>Plains, GA</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$800 per week</t>
+  </si>
+  <si>
+    <t>ecology-hydrology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-individual-placement--natural-resource-technician-plains-georgia/2123066751</t>
+  </si>
+  <si>
+    <t>Animal Care Attendant</t>
+  </si>
+  <si>
+    <t>West Coast Falconry</t>
+  </si>
+  <si>
+    <t>Marysville, CA</t>
+  </si>
+  <si>
+    <t>$18 per hour</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-animal-care-attendant-marysville-california/5177808583</t>
+  </si>
+  <si>
+    <t>Conservation Biologist</t>
+  </si>
+  <si>
+    <t>Mason-Lake Conservation District</t>
+  </si>
+  <si>
+    <t>Scottville, MI</t>
+  </si>
+  <si>
+    <t>$24 - $28 per hour</t>
+  </si>
+  <si>
+    <t>botany-ecology-forestry-restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-biologist-scottville-michigan/7679415709</t>
+  </si>
+  <si>
+    <t>Content Senior Manager</t>
+  </si>
+  <si>
+    <t>Washington Conservation Action</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>$73,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-content-senior-manager-seattle-washington/3243704148</t>
+  </si>
+  <si>
+    <t>Federal Grant Administrator</t>
+  </si>
+  <si>
+    <t>$30 - $33.60 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-federal-grant-administrator-topeka-kansas/9914045740</t>
+  </si>
+  <si>
+    <t>Fisheries Wildlife Biologist I</t>
+  </si>
+  <si>
+    <t>Farlington, KS</t>
+  </si>
+  <si>
+    <t>$24.46 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-wildlife-biologist-i-farlington-kansas/6119764792</t>
+  </si>
+  <si>
+    <t>Foundation Relations Assistant</t>
+  </si>
+  <si>
+    <t>The Public Interest Network</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>The starting annual compensation range for someone with 1-6 years of relevant experience is $40,000-$48,000.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-foundation-relations-assistant-washington-dc/3555000979</t>
+  </si>
+  <si>
+    <t>GS 11 Wildlife Biologist</t>
+  </si>
+  <si>
+    <t>National Park Service</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>$93,000 - $121,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-gs-11-wildlife-biologist-san-francisco-california/4992604030</t>
+  </si>
+  <si>
+    <t>Horticulture Apprenticeship Program Manager</t>
+  </si>
+  <si>
+    <t>Louisville Grows</t>
+  </si>
+  <si>
+    <t>Louisville, KY</t>
+  </si>
+  <si>
+    <t>$50,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-horticulture-apprenticeship-program-manager-louisville-kentucky/7866339414</t>
+  </si>
+  <si>
+    <t>Market-Based PES Instruments Specialist</t>
+  </si>
+  <si>
+    <t>FCF India Pvt. Ltd.</t>
+  </si>
+  <si>
+    <t>Shillong, Asia</t>
+  </si>
+  <si>
+    <t>Commensurate with relevant experience</t>
+  </si>
+  <si>
+    <t>admin-leadership-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-market-based-pes-instruments-specialist-shillong-asia/2471397507</t>
+  </si>
+  <si>
+    <t>Marketing Internship</t>
+  </si>
+  <si>
+    <t>Boundless Impact Research &amp; Analytics</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>This is an unpaid internship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marketing-internship-new-york-new-york/3553913613</t>
+  </si>
+  <si>
+    <t>Member Manager</t>
+  </si>
+  <si>
+    <t>American Conservation Experience (ACE)</t>
+  </si>
+  <si>
+    <t>Fletcher, NC</t>
+  </si>
+  <si>
+    <t>$50,000 - $52,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-member-manager-fletcher-north-carolina/6446736307</t>
+  </si>
+  <si>
+    <t>Molecular Ecologist</t>
+  </si>
+  <si>
+    <t>California Department of Water Resources</t>
+  </si>
+  <si>
+    <t>West Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$53,016 - $111,852 per year</t>
+  </si>
+  <si>
+    <t>ecology-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-molecular-ecologist-west-sacramento-california/2937812082</t>
+  </si>
+  <si>
+    <t>Natural Resources Specialist II - III - IV (Permits and Consultations Coordinator)</t>
+  </si>
+  <si>
+    <t>Texas Parks &amp; Wildlife Department</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>$5,350.87 - $6,776.85 per month</t>
+  </si>
+  <si>
+    <t>fisheries-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-specialist-ii---iii---iv-permits-and-consultations-coordinator-austin-texas/7486535521</t>
+  </si>
+  <si>
+    <t>Outreach Program Assistant</t>
+  </si>
+  <si>
+    <t>International Crane Foundation</t>
+  </si>
+  <si>
+    <t>Decatur, AL</t>
+  </si>
+  <si>
+    <t>$17 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outreach-program-assistant-decatur-alabama/8938216094</t>
+  </si>
+  <si>
+    <t>Parks Resource Specialist</t>
+  </si>
+  <si>
+    <t>Bernalillo County</t>
+  </si>
+  <si>
+    <t>Albuquerque, NM</t>
+  </si>
+  <si>
+    <t>$22.81 - $36.01 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-parks-resource-specialist-albuquerque-new-mexico/5372771986</t>
+  </si>
+  <si>
+    <t>PhD Position Freshwater Mussel Physiology</t>
+  </si>
+  <si>
+    <t>University of South Dakota</t>
+  </si>
+  <si>
+    <t>Vermillion, SD</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>$23,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-phd-position-freshwater-mussel-physiology-vermillion-south-dakota/8856940378</t>
+  </si>
+  <si>
+    <t>Philanthropy Manager (Part Time)</t>
+  </si>
+  <si>
+    <t>Environmental Action Committee of West Marin (EAC)</t>
+  </si>
+  <si>
+    <t>Point Reyes Station, CA</t>
+  </si>
+  <si>
+    <t>$35 - $45 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-philanthropy-manager-part-time-point-reyes-station-california/6014556478</t>
+  </si>
+  <si>
+    <t>Public Lands Manager II</t>
+  </si>
+  <si>
+    <t>$28.65 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-lands-manager-ii-topeka-kansas/8560107476</t>
+  </si>
+  <si>
+    <t>Public Lands Manager III</t>
+  </si>
+  <si>
+    <t>Lecompton, KS</t>
+  </si>
+  <si>
+    <t>$30.83 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-lands-manager-iii-lecompton-kansas/6854085199</t>
+  </si>
+  <si>
+    <t>Quantitative Research Scientist</t>
+  </si>
+  <si>
+    <t>Bird Conservancy of the Rockies</t>
+  </si>
+  <si>
+    <t>Fort Collins, CO</t>
+  </si>
+  <si>
+    <t>$72,000 - $95,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-quantitative-research-scientist-fort-collins-colorado/2294538718</t>
+  </si>
+  <si>
+    <t>Toxics Campaign Director</t>
+  </si>
+  <si>
+    <t>PIRG</t>
+  </si>
+  <si>
+    <t>The target starting compensation for someone with 3-8 years of relevant professional experience is $42,500-$60,000 in the first year.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-toxics-campaign-director-washington-dc/9945165637</t>
+  </si>
+  <si>
+    <t>USDA-ARS Biting Fly Biology Fellowship</t>
+  </si>
+  <si>
+    <t>U.S. Department of Agriculture (USDA)</t>
+  </si>
+  <si>
+    <t>Manhattan, KS</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>Stipend $49,000.00 – $54,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-biting-fly-biology-fellowship-manhattan-kansas/6660941835</t>
+  </si>
+  <si>
+    <t>USDA-ARS Fire Ant Behavior and Chemical Ecology - Post-Bachelor Research Opportunity</t>
+  </si>
+  <si>
+    <t>Gainesville, FL</t>
+  </si>
+  <si>
+    <t>Stipend $3,443.00 Monthly</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-dashboard--opportunity-catalog--about---help-welcome-heathergilliamorauorg-usda-ars-fire-ant-behavior-and-chemical-ecology---post-bachelor-research-opportunity-gainesville-florida/7062412595</t>
+  </si>
+  <si>
+    <t>USDA-ARS Postdoctoral Fellowship for Arbovirus Research</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>Stipend $74,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-postdoctoral-fellowship-for-arbovirus-research-manhattan-kansas/9950491090</t>
+  </si>
+  <si>
+    <t>USDA-ARS Postdoctoral Opportunity in Molecular Plant Pathogen Research</t>
+  </si>
+  <si>
+    <t>New Orleans, LA</t>
+  </si>
+  <si>
+    <t>Stipend $6,223.17 Monthly</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-postdoctoral-opportunity-in-molecular-plant-pathogen-research-new-orleans-louisiana/1303891104</t>
+  </si>
+  <si>
+    <t>USDA-ARS Research Fellowship in Population Genetics and Microbiomes of Invasive Ants</t>
+  </si>
+  <si>
+    <t>Stipend $1,547.51 – $1,547.52 Monthly</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-research-fellowship-in-population-genetics-and-microbiomes-of-invasive-ants-gainesville-florida/3990572718</t>
+  </si>
+  <si>
+    <t>Wildlife Education Curator</t>
+  </si>
+  <si>
+    <t>Arizona Game and Fish Dept</t>
+  </si>
+  <si>
+    <t>Phoenix, AZ</t>
+  </si>
+  <si>
+    <t>$56,098 - $100,989 per year</t>
+  </si>
+  <si>
+    <t>environmental-education-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-education-curator-phoenix-arizona/3748362002</t>
+  </si>
+  <si>
+    <t>Worker's Compensation Specialist</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>$28 - $32 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-workers-compensation-specialist-remote-remote/1273598417</t>
+  </si>
+  <si>
+    <t>Administrative &amp; Operations Assistant, Fab Youth Philly</t>
+  </si>
+  <si>
+    <t>Fab Youth Philly</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a31088c86c1416f8350c06e6e54d9a2-administrative-operations-assistant-fab-youth-philly-fab-youth-philly-philadelphia</t>
+  </si>
+  <si>
+    <t>After School Program Assistant Teacher</t>
+  </si>
+  <si>
+    <t>The Buckley School in the City of New York</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1ed503100ddb48d783a858b7ab068bea-after-school-program-assistant-teacher-the-buckley-school-in-the-city-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Analyst, Housing Resources</t>
+  </si>
+  <si>
+    <t>The Kelsey</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 97000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disability, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7efec459376f4ac4bb92c306139e6e86-analyst-housing-resources-the-kelsey-san-francisco</t>
+  </si>
+  <si>
+    <t>Artist-Centered Program Manager</t>
+  </si>
+  <si>
+    <t>Joan Mitchell Foundation</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8eec6db3180c4e0fa6763680c9aeec63-artist-centered-program-manager-joan-mitchell-foundation-new-orleans</t>
+  </si>
+  <si>
+    <t>Assistant Director of Individual Giving and Events</t>
+  </si>
+  <si>
+    <t>University Settlement Society of New York</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc0635cd51b3414594cf421e727c519f-assistant-director-of-individual-giving-and-events-university-settlement-society-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Attorney - Program Counsel (Michigan Based)</t>
+  </si>
+  <si>
+    <t>Chicago Lawyers' Committee For Civil Rights Under Law, Inc.</t>
+  </si>
+  <si>
+    <t>Remote (Michigan)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Race Ethnicity, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/22ce5dcb77ea4d3cb01498b3bcf530c8-attorney-program-counsel-michigan-based-chicago-lawyers-committee-for-civil-rights-under-law-inc-chicago</t>
+  </si>
+  <si>
+    <t>Attorney - Program Counsel (Wisconsin Based)</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Civic Engagement, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c92ef5a74b424887994dd7780162b30d-attorney-program-counsel-wisconsin-based-chicago-lawyers-committee-for-civil-rights-under-law-inc-chicago</t>
+  </si>
+  <si>
+    <t>California Senior Finance Director</t>
+  </si>
+  <si>
+    <t>Working Families</t>
+  </si>
+  <si>
+    <t>USD 86400.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b04b1ffc8b9400f934d850d0841511c-california-senior-finance-director-working-families-kings-county</t>
+  </si>
+  <si>
+    <t>Case Manager, HomeStart Program</t>
+  </si>
+  <si>
+    <t>Doorways</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b13999c74a34bdda052444afc1fe7c9-case-manager-homestart-program-doorways-arlington</t>
+  </si>
+  <si>
+    <t>Chief Advancement Officer</t>
+  </si>
+  <si>
+    <t>Diabetes Research Institute Foundation</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8bad8de7acd74ed6a883eeec0292b0f8-chief-advancement-officer-diabetes-research-institute-foundation-miami</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>The Ember Alliance</t>
+  </si>
+  <si>
+    <t>USD 100880.00 - 100880.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4aae787fc2444256988f2223ee04464a-chief-financial-officer-the-ember-alliance-fort-collins</t>
+  </si>
+  <si>
+    <t>Chief Housing Development Officer</t>
+  </si>
+  <si>
+    <t>SOME (So Others Might Eat)</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 168376.00 - 178289.28/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29e006b18ace44ff9b11b5ceb5c6c9dd-chief-housing-development-officer-some-so-others-might-eat-washington</t>
+  </si>
+  <si>
+    <t>Clinic Coordinator</t>
+  </si>
+  <si>
+    <t>Remote Area Medical</t>
+  </si>
+  <si>
+    <t>Rockford, Tennessee</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/327cd2a5564c4e36b9937accc96bed92-clinic-coordinator-remote-area-medical-rockford</t>
+  </si>
+  <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>Oberkotter Foundation</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4a5c3d8fed76470eb81a529ef595adee-communications-associate-oberkotter-foundation-philadelphia</t>
+  </si>
+  <si>
+    <t>Literacy Inc. (LINC)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de22c734f34b4d83abce3320f6afa8ed-communications-associate-literacy-inc-linc-new-york</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>Bedford 2030</t>
+  </si>
+  <si>
+    <t>Katonah, New York</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ff7c00d08ac340fb8fd881daf971c4ba-communications-manager-bedford-2030-katonah</t>
+  </si>
+  <si>
+    <t>Communications Specialist</t>
+  </si>
+  <si>
+    <t>Grantmakers In Health</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b47f8384e3146c386c0ecc407096e25-communications-specialist-grantmakers-in-health-washington</t>
+  </si>
+  <si>
+    <t>Community Resource Navigator</t>
+  </si>
+  <si>
+    <t>Annapolis Immigration Justice Network</t>
+  </si>
+  <si>
+    <t>Annapolis, Maryland</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe8c6956d867432288efa98f1b9ef071-community-resource-navigator-annapolis-immigration-justice-network-annapolis</t>
+  </si>
+  <si>
+    <t>CONSUMER STAFF ATTORNEY – BROCKTON LAW OFFICE</t>
+  </si>
+  <si>
+    <t>South Coastal Counties Legal Services Inc.</t>
+  </si>
+  <si>
+    <t>Brockton, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 86500.00 - 113000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a144bd4ea1644b3697c29fd75121116f-consumer-staff-attorney-brockton-law-office-south-coastal-counties-legal-services-inc-brockton</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>CommonLit, Inc.</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/69aeec45e8b54b28874d5d312ddb5f74-controller-commonlit-inc-washington</t>
+  </si>
+  <si>
+    <t>Controller / Director of Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/71a307606222445e956ea7e32f50ce07-controller-director-of-finance-diabetes-research-institute-foundation-miami</t>
+  </si>
+  <si>
+    <t>CORE Scheduling Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/d3f2160f6feb4f27b703623ae5246e3c-core-scheduling-coordinator-remote-area-medical-rockford</t>
+  </si>
+  <si>
+    <t>Country Manager, US</t>
+  </si>
+  <si>
+    <t>350.org</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b77e8c223e2e4d1db68b8ce04751d3e3-country-manager-us-350org-washington</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Kate's Club</t>
+  </si>
+  <si>
+    <t>Brookhaven, Georgia</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3131f646135445c997bfa25b1925c9aa-development-manager-kates-club-brookhaven</t>
+  </si>
+  <si>
+    <t>Director of Corporate and Foundation Relations</t>
+  </si>
+  <si>
+    <t>National Breast Cancer Coalition</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f121784393c9425abd6ae7d95f96b223-director-of-corporate-and-foundation-relations-national-breast-cancer-coalition-washington</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Ramat Shalom Beth Israel</t>
+  </si>
+  <si>
+    <t>Plantation, Florida</t>
+  </si>
+  <si>
+    <t>Education, Family, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1729e7de045d47fb895be04c0b992b3b-director-of-development-ramat-shalom-beth-israel-plantation</t>
+  </si>
+  <si>
+    <t>City Year Kansas City</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri</t>
+  </si>
+  <si>
+    <t>USD 79000.00 - 83000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42f93662c312462c8927c3a19e913bfd-director-of-development-city-year-kansas-city-kansas-city</t>
+  </si>
+  <si>
+    <t>Converge: Partners in Access</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Women, Reproductive Health Rights, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/874a04dc3fd140d894b4799afd3f689a-director-of-development-converge-partners-in-access-ridgeland</t>
+  </si>
+  <si>
+    <t>Director of People &amp; Operations</t>
+  </si>
+  <si>
+    <t>Ayuda</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 128000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3eaf091a69b045db9db6ba6068735db5-director-of-people-operations-ayuda-washington</t>
+  </si>
+  <si>
+    <t>Director of Social Work Services</t>
+  </si>
+  <si>
+    <t>Educational Alliance</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09150c0346c74f76b0ac8e6bd12c5a01-director-of-social-work-services-educational-alliance-new-york</t>
+  </si>
+  <si>
+    <t>Director, Education</t>
+  </si>
+  <si>
+    <t>Plastics Industry Association (PLASTICS)</t>
+  </si>
+  <si>
+    <t>USD 113000.00 - 141000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ffc06a9a3ed1498db5eeb849fedfeee6-director-education-plastics-industry-association-plastics-washington</t>
+  </si>
+  <si>
+    <t>Discovery Paralegal, Queens Criminal Practice</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac0ab3e1f3a44ce294a23251c12efa6e-discovery-paralegal-queens-criminal-practice-brooklyn-defender-services-queens-county</t>
+  </si>
+  <si>
+    <t>Donor Relations Executive, Bangalore</t>
+  </si>
+  <si>
+    <t>Ground Zero</t>
+  </si>
+  <si>
+    <t>Bangalore, Bangalore, IN</t>
+  </si>
+  <si>
+    <t>INR 350000.00 - 450000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eef1207dd8f8402fabcafba7f175d93a-donor-relations-executive-bangalore-ground-zero-bangalore</t>
+  </si>
+  <si>
+    <t>DSV Advocate &amp; Navigator</t>
+  </si>
+  <si>
+    <t>YWCA of Greater Portland</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 27.75 - 27.75/hour</t>
+  </si>
+  <si>
+    <t>Economic Development, Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8b274e71e4bc4a168d86a9bed76fcbec-dsv-advocate-navigator-ywca-of-greater-portland-portland</t>
+  </si>
+  <si>
+    <t>Entry Level Attorney, Criminal Defense Practice, September 2027, Brooklyn Office</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 99910.00 - 99910.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad1cc3b64c3d40f49f6c398426cdad7b-entry-level-attorney-criminal-defense-practice-september-2027-brooklyn-office-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
+    <t>Entry Level Attorney, Criminal Defense Practice, September 2027, Queens Office</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61233e240d544361b1a3c8b284dc9d5e-entry-level-attorney-criminal-defense-practice-september-2027-queens-office-brooklyn-defender-services-queens-county</t>
+  </si>
+  <si>
+    <t>Executive Associate</t>
+  </si>
+  <si>
+    <t>The One America Movement</t>
+  </si>
+  <si>
+    <t>Bowie, Maryland</t>
+  </si>
+  <si>
+    <t>USD 52800.00 - 68600.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6559b59b6ecc471088988d3780251778-executive-associate-the-one-america-movement-bowie</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Camp for All Kids</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e6a6a0f76cd414fbeff23df910a2596-executive-director-camp-for-all-kids-chicago</t>
+  </si>
+  <si>
+    <t>Woori Juntos</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba755a9ebc7f4e4fad20053d4b0bb641-executive-director-woori-juntos-houston</t>
+  </si>
+  <si>
+    <t>Parenting Connection of Monterey County</t>
+  </si>
+  <si>
+    <t>Salinas, California</t>
+  </si>
+  <si>
+    <t>USD 96000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Mental Health, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/48a008ab73b145739391c2ce98e036b8-executive-director-parenting-connection-of-monterey-county-salinas</t>
+  </si>
+  <si>
+    <t>Public Assets Institute</t>
+  </si>
+  <si>
+    <t>Montpelier, VT</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3654068458ab40b580ec8bd0bb73f19c-executive-director-public-assets-institute-montpelier</t>
+  </si>
+  <si>
+    <t>Tilth Alliance</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd44f0536ecf4bcc8e399dfa0db1f47a-executive-director-tilth-alliance-seattle</t>
+  </si>
+  <si>
+    <t>50 Mile March Foundation</t>
+  </si>
+  <si>
+    <t>Bellevue, Nebraska</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7901ec219eaf45df8b5570dc09930d9d-executive-director-50-mile-march-foundation-bellevue</t>
+  </si>
+  <si>
+    <t>Gateway Early Childhood Alliance</t>
+  </si>
+  <si>
+    <t>St. Louis, Missouri</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4b7a3f60cfa242aa891e4f1066422523-executive-director-gateway-early-childhood-alliance-st-louis</t>
+  </si>
+  <si>
+    <t>Finance &amp; Admin Associate, New Delhi</t>
+  </si>
+  <si>
+    <t>Delhi, Delhi, IN</t>
+  </si>
+  <si>
+    <t>INR 500000.00 - 600000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b53339688071433dbddc0e89f6f5cdc0-finance-admin-associate-new-delhi-ground-zero-delhi</t>
+  </si>
+  <si>
+    <t>Freelance Online Event Host</t>
+  </si>
+  <si>
+    <t>70 Faces Media</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/128a3401fb53472597ca78180ce8edd9-freelance-online-event-host-70-faces-media-new-york</t>
+  </si>
+  <si>
+    <t>Grants &amp; Operations Manager</t>
+  </si>
+  <si>
+    <t>Woodcock Foundation</t>
+  </si>
+  <si>
+    <t>Remote (New York, New York)</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/816ab479d1094cd18b30ce725aa0c15c-grants-operations-manager-woodcock-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Grants and Development Manager</t>
+  </si>
+  <si>
+    <t>Formerly Incarcerated, Convicted People &amp; Families Movement (FICPFM)</t>
+  </si>
+  <si>
+    <t>USD 97000.00 - 97000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/752ef1be8f0148fb94776429430c1486-grants-and-development-manager-formerly-incarcerated-convicted-people-families-movement-ficpfm-windermere</t>
+  </si>
+  <si>
+    <t>Health Education Program Coordinator – YMSM Program</t>
+  </si>
+  <si>
+    <t>AIDS Center of Queens County, Inc. - ACQC</t>
+  </si>
+  <si>
+    <t>USD 66300.00 - 66300.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Lgbtq, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4d49ccb3329a4d95aed316c9b2c2c31a-health-education-program-coordinator-ymsm-program-aids-center-of-queens-county-inc-acqc-queens-county</t>
+  </si>
+  <si>
+    <t>HUD-Certified Foreclosure Prevention Housing Counselor</t>
+  </si>
+  <si>
+    <t>Housing Help Inc.</t>
+  </si>
+  <si>
+    <t>East Northport, New York</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Financial Literacy Personal Finance, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c073361610b4d5bac7efb3b892d7e6f-hud-certified-foreclosure-prevention-housing-counselor-housing-help-inc-east-northport</t>
+  </si>
+  <si>
+    <t>Individual Gifts Officer</t>
+  </si>
+  <si>
+    <t>Citizens for Responsibility and Ethics in Washington</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5824b04c0ff0478dbffe027848b5efde-individual-gifts-officer-citizens-for-responsibility-and-ethics-in-washington-washington</t>
+  </si>
+  <si>
+    <t>Launch Fellow (Full-Time, Paid)</t>
+  </si>
+  <si>
+    <t>Rochester Education and Development for Youth (READY)</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a51978ec39b54b118284fed88b5eb8e7-launch-fellow-full-time-paid-rochester-education-and-development-for-youth-ready-rochester</t>
+  </si>
+  <si>
+    <t>Lead Tenant Organizer and Civic Engagement Project Supervisor</t>
+  </si>
+  <si>
+    <t>Mass. Alliance of HUD Tenants</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9bd59a29e9e447d7a332eaea4f4af8b3-lead-tenant-organizer-and-civic-engagement-project-supervisor-mass-alliance-of-hud-tenants-boston</t>
+  </si>
+  <si>
+    <t>Leadership Gift Officer, Graduate School of Journalism</t>
+  </si>
+  <si>
+    <t>Columbia University HR</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55eb4c5da55f47438184ce1f44a7090d-leadership-gift-officer-graduate-school-of-journalism-columbia-university-hr-new-york</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>CodeAI</t>
+  </si>
+  <si>
+    <t>USD 99000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/411f2f6fa6c44863bff90d08b9f0c7ac-major-gifts-officer-codeai-seattle</t>
+  </si>
+  <si>
+    <t>Operations and Finance Administration Manager</t>
+  </si>
+  <si>
+    <t>Israel Policy Forum</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62aa7952b9124b53991ae3d7ec9dfd17-operations-and-finance-administration-manager-israel-policy-forum-new-york</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Texas Observer</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Media, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/208da3d24827422aad798b409d164b2a-operations-manager-texas-observer-austin</t>
+  </si>
+  <si>
+    <t>Operations Manager, Events &amp; Revenue</t>
+  </si>
+  <si>
+    <t>BRIC</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80818b351b3d4006b44f1222edd413bc-operations-manager-events-revenue-bric-kings-county</t>
+  </si>
+  <si>
+    <t>Operations Manager, Facilities &amp; Building Management</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d70377dee6d4454995b68d9a6bfc66e-operations-manager-facilities-building-management-bric-kings-county</t>
+  </si>
+  <si>
+    <t>Part-Time Youth Instructor — No Boatbuilding Experience Required</t>
+  </si>
+  <si>
+    <t>Brooklyn Boatworks</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0af8d222107847a7b54fc5ed6ab91f71-part-time-youth-instructor-no-boatbuilding-experience-required-brooklyn-boatworks-kings-county</t>
+  </si>
+  <si>
+    <t>Payment Processing Manager</t>
+  </si>
+  <si>
+    <t>Way Finders, Inc.</t>
+  </si>
+  <si>
+    <t>Springfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 77000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d56f5b8968794acb89f6d034b7bcecde-payment-processing-manager-way-finders-inc-springfield</t>
+  </si>
+  <si>
+    <t>Peer Specialist</t>
+  </si>
+  <si>
+    <t>Youth Justice Network</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da78c580d556437eb9be6864bcb5af5d-peer-specialist-youth-justice-network-new-york</t>
+  </si>
+  <si>
+    <t>Pessoa Assessora Administrativa Financeira I</t>
+  </si>
+  <si>
+    <t>Instituto de Defesa do Direito de Defesa - Marcio Thomaz Bastos</t>
+  </si>
+  <si>
+    <t>São Paulo, São Paulo, BR</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3d52e6cd9ecf48daaf0d1426ffc6fceb-pessoa-assessora-administrativa-financeira-i-instituto-de-defesa-do-direito-de-defesa-marcio-thomaz-bastos-sao-paulo</t>
+  </si>
+  <si>
+    <t>Programs Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9064a01fec8e4849a6e082fbb6f24656-programs-manager-bedford-2030-katonah</t>
+  </si>
+  <si>
+    <t>Project Coordinator, K-12 Career Navigation System</t>
+  </si>
+  <si>
+    <t>QA Commons</t>
+  </si>
+  <si>
+    <t>USD 44.00 - 44.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e4409e7968a4f1cb3719b2f61d4a07c-project-coordinator-k-12-career-navigation-system-qa-commons-st-helena</t>
+  </si>
+  <si>
+    <t>Senior Accountant / Operations Specialist</t>
+  </si>
+  <si>
+    <t>USD 58240.00 - 66560.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0ef5f575326d4b8da966ab43bb91fc3f-senior-accountant-operations-specialist-the-ember-alliance-fort-collins</t>
+  </si>
+  <si>
+    <t>Senior Attorney, Capacity Building</t>
+  </si>
+  <si>
+    <t>The Resurrection Project</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f84103a38d0e482fb583157d0d745512-senior-attorney-capacity-building-the-resurrection-project-chicago</t>
+  </si>
+  <si>
+    <t>Senior Campaign Organizer</t>
+  </si>
+  <si>
+    <t>Association for Neighborhood and Housing Development</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 89000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6f5706812394133baf21b67c7637c5e-senior-campaign-organizer-association-for-neighborhood-and-housing-development-new-york</t>
+  </si>
+  <si>
+    <t>Senior Development Manager</t>
+  </si>
+  <si>
+    <t>The Acceleration Project</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>Philanthropy, Race Ethnicity, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c5e5fdc97c640e9a58ac05361939c4d-senior-development-manager-the-acceleration-project-scarsdale</t>
+  </si>
+  <si>
+    <t>Senior Manager, Development - California</t>
+  </si>
+  <si>
+    <t>Partnership for Public Service</t>
+  </si>
+  <si>
+    <t>Remote (San Francisco, California)</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5adab707c844d4595ab7bf05c1be2f0-senior-manager-development-california-partnership-for-public-service-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Manager, Nonprofit Member Experience</t>
+  </si>
+  <si>
+    <t>Good360</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disaster Relief, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a57d3f82c87a4c068245b5562079b5e0-senior-manager-nonprofit-member-experience-good360-alexandria</t>
+  </si>
+  <si>
+    <t>Senior Policy Advisor</t>
+  </si>
+  <si>
+    <t>ControlAI</t>
+  </si>
+  <si>
+    <t>USD 160000.00/year</t>
+  </si>
+  <si>
+    <t>Science Technology, Civic Engagement, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc7e821d3a644b2cb41a25e740a84623-senior-policy-advisor-controlai-washington</t>
+  </si>
+  <si>
+    <t>Senior Project Manager</t>
+  </si>
+  <si>
+    <t>Immigrant Legal Resource Center</t>
+  </si>
+  <si>
+    <t>Remote (Fresno, California)</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27f92264bec34cc9908b94a78456e7de-senior-project-manager-immigrant-legal-resource-center-fresno</t>
+  </si>
+  <si>
+    <t>Remote (Los Angeles, California)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/081e381ca4fb4e39b0ce46415897cc2a-senior-project-manager-immigrant-legal-resource-center-los-angeles</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ad52abddd0e4d20a2275eef34bda964-senior-project-manager-immigrant-legal-resource-center-san-francisco</t>
+  </si>
+  <si>
+    <t>Social Media Coordinator</t>
+  </si>
+  <si>
+    <t>The Cathedral Church of Saint John the Divine of New York</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b214686fa92542a294cfc618bfee4138-social-media-coordinator-the-cathedral-church-of-saint-john-the-divine-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Catholic Charities Archdiocese of NY</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 84590.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a9762df7c75494b9220bd655e55062e-staff-attorney-catholic-charities-archdiocese-of-ny-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney - Grandparents Raising Grandchildren</t>
+  </si>
+  <si>
+    <t>SeniorLAW Center</t>
+  </si>
+  <si>
+    <t>USD 66000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Human Rights Civil Liberties, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f8f88269bd240ca97638fa5662dc12f-staff-attorney-grandparents-raising-grandchildren-seniorlaw-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Hogar [Home] Program</t>
+  </si>
+  <si>
+    <t>National Center for LGBTQ Rights</t>
+  </si>
+  <si>
+    <t>USD 95143.00 - 115857.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6fd345f9623453eae81220408003740-staff-attorney-hogar-home-program-national-center-for-lgbtq-rights-san-francisco</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Victim Services</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0bd370a74bb84f50bb06a6e119b315ad-staff-attorney-victim-services-seniorlaw-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Strategic Operations Administrator</t>
+  </si>
+  <si>
+    <t>Gemstones in the Sun</t>
+  </si>
+  <si>
+    <t>USD 0.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Entrepreneurship, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/81b061e297b94dec8aa62fc38944afa2-strategic-operations-administrator-gemstones-in-the-sun-silver-spring</t>
+  </si>
+  <si>
+    <t>Student and Family Engagement Service Member</t>
+  </si>
+  <si>
+    <t>Kid Power, Inc.</t>
+  </si>
+  <si>
+    <t>USD 2000.00 - 2000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c174e828ef11477c8accf7c9462784c3-student-and-family-engagement-service-member-kid-power-inc-washington</t>
+  </si>
+  <si>
+    <t>Vice President of Finance and Operations</t>
+  </si>
+  <si>
+    <t>Forest Society of Maine</t>
+  </si>
+  <si>
+    <t>Bangor, Maine</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/631f0111ffcc49af920c13924b58ae6a-vice-president-of-finance-and-operations-forest-society-of-maine-bangor</t>
+  </si>
+  <si>
+    <t>Vice President, Strategic Partnerships &amp; Development</t>
+  </si>
+  <si>
+    <t>California Charter Schools Association</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 129560.00 - 150570.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e3c1358aa80946789c3ffff64650f9f8-vice-president-strategic-partnerships-development-california-charter-schools-association-los-angeles</t>
+  </si>
+  <si>
+    <t>Water, Sanitation &amp; Hygiene (WASH) Advisor</t>
+  </si>
+  <si>
+    <t>Medair</t>
+  </si>
+  <si>
+    <t>Kharkiv, Kharkiv Oblast, UA</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Water Sanitation, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdd874a1f7674ce2a7ab08bc72e26abd-water-sanitation-hygiene-wash-advisor-medair-kharkiv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1785,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1811,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2193,754 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" t="s">
+        <v>133</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>137</v>
+      </c>
+      <c r="F25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" t="s">
+        <v>133</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27" t="s">
+        <v>133</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" t="s">
+        <v>133</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" t="s">
+        <v>133</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" t="s">
+        <v>163</v>
+      </c>
+      <c r="C31" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" t="s">
+        <v>166</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>168</v>
+      </c>
+      <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
+        <v>169</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>170</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +2996,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3035,2050 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F4" t="s">
+        <v>190</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" t="s">
+        <v>196</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" t="s">
+        <v>206</v>
+      </c>
+      <c r="F7" t="s">
+        <v>207</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" t="s">
+        <v>206</v>
+      </c>
+      <c r="F8" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" t="s">
+        <v>227</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>229</v>
+      </c>
+      <c r="B12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" t="s">
+        <v>231</v>
+      </c>
+      <c r="F12" t="s">
+        <v>201</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" t="s">
+        <v>236</v>
+      </c>
+      <c r="F13" t="s">
+        <v>237</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>239</v>
+      </c>
+      <c r="B14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" t="s">
+        <v>241</v>
+      </c>
+      <c r="D14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" t="s">
+        <v>201</v>
+      </c>
+      <c r="F14" t="s">
+        <v>201</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15" t="s">
+        <v>188</v>
+      </c>
+      <c r="E15" t="s">
+        <v>245</v>
+      </c>
+      <c r="F15" t="s">
+        <v>246</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B16" t="s">
+        <v>248</v>
+      </c>
+      <c r="C16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" t="s">
+        <v>188</v>
+      </c>
+      <c r="E16" t="s">
+        <v>249</v>
+      </c>
+      <c r="F16" t="s">
+        <v>250</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>252</v>
+      </c>
+      <c r="B17" t="s">
+        <v>253</v>
+      </c>
+      <c r="C17" t="s">
+        <v>254</v>
+      </c>
+      <c r="D17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" t="s">
+        <v>255</v>
+      </c>
+      <c r="F17" t="s">
+        <v>256</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>258</v>
+      </c>
+      <c r="B18" t="s">
+        <v>259</v>
+      </c>
+      <c r="C18" t="s">
+        <v>235</v>
+      </c>
+      <c r="D18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E18" t="s">
+        <v>260</v>
+      </c>
+      <c r="F18" t="s">
+        <v>201</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>262</v>
+      </c>
+      <c r="B19" t="s">
+        <v>263</v>
+      </c>
+      <c r="C19" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" t="s">
+        <v>265</v>
+      </c>
+      <c r="F19" t="s">
+        <v>266</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>268</v>
+      </c>
+      <c r="B20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" t="s">
+        <v>270</v>
+      </c>
+      <c r="D20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E20" t="s">
+        <v>271</v>
+      </c>
+      <c r="F20" t="s">
+        <v>272</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>274</v>
+      </c>
+      <c r="B21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C21" t="s">
+        <v>187</v>
+      </c>
+      <c r="D21" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" t="s">
+        <v>276</v>
+      </c>
+      <c r="F21" t="s">
+        <v>277</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>279</v>
+      </c>
+      <c r="B22" t="s">
+        <v>225</v>
+      </c>
+      <c r="C22" t="s">
+        <v>226</v>
+      </c>
+      <c r="D22" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" t="s">
+        <v>201</v>
+      </c>
+      <c r="F22" t="s">
+        <v>227</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>281</v>
+      </c>
+      <c r="B23" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" t="s">
+        <v>201</v>
+      </c>
+      <c r="F23" t="s">
+        <v>201</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>283</v>
+      </c>
+      <c r="B24" t="s">
+        <v>284</v>
+      </c>
+      <c r="C24" t="s">
+        <v>187</v>
+      </c>
+      <c r="D24" t="s">
+        <v>285</v>
+      </c>
+      <c r="E24" t="s">
+        <v>286</v>
+      </c>
+      <c r="F24" t="s">
+        <v>287</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>289</v>
+      </c>
+      <c r="B25" t="s">
+        <v>290</v>
+      </c>
+      <c r="C25" t="s">
+        <v>291</v>
+      </c>
+      <c r="D25" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" t="s">
+        <v>292</v>
+      </c>
+      <c r="F25" t="s">
+        <v>293</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>295</v>
+      </c>
+      <c r="B26" t="s">
+        <v>296</v>
+      </c>
+      <c r="C26" t="s">
+        <v>235</v>
+      </c>
+      <c r="D26" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" t="s">
+        <v>297</v>
+      </c>
+      <c r="F26" t="s">
+        <v>298</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>300</v>
+      </c>
+      <c r="B27" t="s">
+        <v>301</v>
+      </c>
+      <c r="C27" t="s">
+        <v>302</v>
+      </c>
+      <c r="D27" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" t="s">
+        <v>201</v>
+      </c>
+      <c r="F27" t="s">
+        <v>303</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>300</v>
+      </c>
+      <c r="B28" t="s">
+        <v>305</v>
+      </c>
+      <c r="C28" t="s">
+        <v>306</v>
+      </c>
+      <c r="D28" t="s">
+        <v>188</v>
+      </c>
+      <c r="E28" t="s">
+        <v>307</v>
+      </c>
+      <c r="F28" t="s">
+        <v>308</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B29" t="s">
+        <v>310</v>
+      </c>
+      <c r="C29" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" t="s">
+        <v>311</v>
+      </c>
+      <c r="F29" t="s">
+        <v>312</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>314</v>
+      </c>
+      <c r="B30" t="s">
+        <v>315</v>
+      </c>
+      <c r="C30" t="s">
+        <v>235</v>
+      </c>
+      <c r="D30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" t="s">
+        <v>316</v>
+      </c>
+      <c r="F30" t="s">
+        <v>317</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>319</v>
+      </c>
+      <c r="B31" t="s">
+        <v>320</v>
+      </c>
+      <c r="C31" t="s">
+        <v>181</v>
+      </c>
+      <c r="D31" t="s">
+        <v>285</v>
+      </c>
+      <c r="E31" t="s">
+        <v>321</v>
+      </c>
+      <c r="F31" t="s">
+        <v>322</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>324</v>
+      </c>
+      <c r="B32" t="s">
+        <v>325</v>
+      </c>
+      <c r="C32" t="s">
+        <v>235</v>
+      </c>
+      <c r="D32" t="s">
+        <v>188</v>
+      </c>
+      <c r="E32" t="s">
+        <v>326</v>
+      </c>
+      <c r="F32" t="s">
+        <v>201</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>328</v>
+      </c>
+      <c r="B33" t="s">
+        <v>329</v>
+      </c>
+      <c r="C33" t="s">
+        <v>330</v>
+      </c>
+      <c r="D33" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" t="s">
+        <v>331</v>
+      </c>
+      <c r="F33" t="s">
+        <v>332</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>334</v>
+      </c>
+      <c r="B34" t="s">
+        <v>335</v>
+      </c>
+      <c r="C34" t="s">
+        <v>336</v>
+      </c>
+      <c r="D34" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" t="s">
+        <v>337</v>
+      </c>
+      <c r="F34" t="s">
+        <v>338</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>340</v>
+      </c>
+      <c r="B35" t="s">
+        <v>341</v>
+      </c>
+      <c r="C35" t="s">
+        <v>342</v>
+      </c>
+      <c r="D35" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" t="s">
+        <v>343</v>
+      </c>
+      <c r="F35" t="s">
+        <v>344</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>346</v>
+      </c>
+      <c r="B36" t="s">
+        <v>329</v>
+      </c>
+      <c r="C36" t="s">
+        <v>347</v>
+      </c>
+      <c r="D36" t="s">
+        <v>188</v>
+      </c>
+      <c r="E36" t="s">
+        <v>348</v>
+      </c>
+      <c r="F36" t="s">
+        <v>332</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>350</v>
+      </c>
+      <c r="B37" t="s">
+        <v>329</v>
+      </c>
+      <c r="C37" t="s">
+        <v>330</v>
+      </c>
+      <c r="D37" t="s">
+        <v>188</v>
+      </c>
+      <c r="E37" t="s">
+        <v>348</v>
+      </c>
+      <c r="F37" t="s">
+        <v>332</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>352</v>
+      </c>
+      <c r="B38" t="s">
+        <v>353</v>
+      </c>
+      <c r="C38" t="s">
+        <v>354</v>
+      </c>
+      <c r="D38" t="s">
+        <v>188</v>
+      </c>
+      <c r="E38" t="s">
+        <v>355</v>
+      </c>
+      <c r="F38" t="s">
+        <v>356</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>358</v>
+      </c>
+      <c r="B39" t="s">
+        <v>359</v>
+      </c>
+      <c r="C39" t="s">
+        <v>360</v>
+      </c>
+      <c r="D39" t="s">
+        <v>188</v>
+      </c>
+      <c r="E39" t="s">
+        <v>361</v>
+      </c>
+      <c r="F39" t="s">
+        <v>362</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>358</v>
+      </c>
+      <c r="B40" t="s">
+        <v>364</v>
+      </c>
+      <c r="C40" t="s">
+        <v>365</v>
+      </c>
+      <c r="D40" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" t="s">
+        <v>366</v>
+      </c>
+      <c r="F40" t="s">
+        <v>367</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>358</v>
+      </c>
+      <c r="B41" t="s">
+        <v>369</v>
+      </c>
+      <c r="C41" t="s">
+        <v>370</v>
+      </c>
+      <c r="D41" t="s">
+        <v>188</v>
+      </c>
+      <c r="E41" t="s">
+        <v>371</v>
+      </c>
+      <c r="F41" t="s">
+        <v>372</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>358</v>
+      </c>
+      <c r="B42" t="s">
+        <v>374</v>
+      </c>
+      <c r="C42" t="s">
+        <v>375</v>
+      </c>
+      <c r="D42" t="s">
+        <v>188</v>
+      </c>
+      <c r="E42" t="s">
+        <v>376</v>
+      </c>
+      <c r="F42" t="s">
+        <v>377</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>358</v>
+      </c>
+      <c r="B43" t="s">
+        <v>379</v>
+      </c>
+      <c r="C43" t="s">
+        <v>380</v>
+      </c>
+      <c r="D43" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43" t="s">
+        <v>381</v>
+      </c>
+      <c r="F43" t="s">
+        <v>382</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>358</v>
+      </c>
+      <c r="B44" t="s">
+        <v>384</v>
+      </c>
+      <c r="C44" t="s">
+        <v>385</v>
+      </c>
+      <c r="D44" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" t="s">
+        <v>386</v>
+      </c>
+      <c r="F44" t="s">
+        <v>387</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>358</v>
+      </c>
+      <c r="B45" t="s">
+        <v>389</v>
+      </c>
+      <c r="C45" t="s">
+        <v>390</v>
+      </c>
+      <c r="D45" t="s">
+        <v>188</v>
+      </c>
+      <c r="E45" t="s">
+        <v>391</v>
+      </c>
+      <c r="F45" t="s">
+        <v>308</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>393</v>
+      </c>
+      <c r="B46" t="s">
+        <v>335</v>
+      </c>
+      <c r="C46" t="s">
+        <v>394</v>
+      </c>
+      <c r="D46" t="s">
+        <v>188</v>
+      </c>
+      <c r="E46" t="s">
+        <v>395</v>
+      </c>
+      <c r="F46" t="s">
+        <v>338</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>397</v>
+      </c>
+      <c r="B47" t="s">
+        <v>398</v>
+      </c>
+      <c r="C47" t="s">
+        <v>187</v>
+      </c>
+      <c r="D47" t="s">
+        <v>399</v>
+      </c>
+      <c r="E47" t="s">
+        <v>400</v>
+      </c>
+      <c r="F47" t="s">
+        <v>401</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>403</v>
+      </c>
+      <c r="B48" t="s">
+        <v>404</v>
+      </c>
+      <c r="C48" t="s">
+        <v>405</v>
+      </c>
+      <c r="D48" t="s">
+        <v>188</v>
+      </c>
+      <c r="E48" t="s">
+        <v>406</v>
+      </c>
+      <c r="F48" t="s">
+        <v>407</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>409</v>
+      </c>
+      <c r="B49" t="s">
+        <v>410</v>
+      </c>
+      <c r="C49" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" t="s">
+        <v>188</v>
+      </c>
+      <c r="E49" t="s">
+        <v>411</v>
+      </c>
+      <c r="F49" t="s">
+        <v>412</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>414</v>
+      </c>
+      <c r="B50" t="s">
+        <v>415</v>
+      </c>
+      <c r="C50" t="s">
+        <v>330</v>
+      </c>
+      <c r="D50" t="s">
+        <v>188</v>
+      </c>
+      <c r="E50" t="s">
+        <v>416</v>
+      </c>
+      <c r="F50" t="s">
+        <v>417</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>419</v>
+      </c>
+      <c r="B51" t="s">
+        <v>420</v>
+      </c>
+      <c r="C51" t="s">
+        <v>421</v>
+      </c>
+      <c r="D51" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51" t="s">
+        <v>422</v>
+      </c>
+      <c r="F51" t="s">
+        <v>423</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>425</v>
+      </c>
+      <c r="B52" t="s">
+        <v>426</v>
+      </c>
+      <c r="C52" t="s">
+        <v>235</v>
+      </c>
+      <c r="D52" t="s">
+        <v>188</v>
+      </c>
+      <c r="E52" t="s">
+        <v>427</v>
+      </c>
+      <c r="F52" t="s">
+        <v>428</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>430</v>
+      </c>
+      <c r="B53" t="s">
+        <v>431</v>
+      </c>
+      <c r="C53" t="s">
+        <v>432</v>
+      </c>
+      <c r="D53" t="s">
+        <v>188</v>
+      </c>
+      <c r="E53" t="s">
+        <v>433</v>
+      </c>
+      <c r="F53" t="s">
+        <v>434</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>436</v>
+      </c>
+      <c r="B54" t="s">
+        <v>437</v>
+      </c>
+      <c r="C54" t="s">
+        <v>438</v>
+      </c>
+      <c r="D54" t="s">
+        <v>188</v>
+      </c>
+      <c r="E54" t="s">
+        <v>439</v>
+      </c>
+      <c r="F54" t="s">
+        <v>440</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>442</v>
+      </c>
+      <c r="B55" t="s">
+        <v>443</v>
+      </c>
+      <c r="C55" t="s">
+        <v>181</v>
+      </c>
+      <c r="D55" t="s">
+        <v>188</v>
+      </c>
+      <c r="E55" t="s">
+        <v>444</v>
+      </c>
+      <c r="F55" t="s">
+        <v>445</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>447</v>
+      </c>
+      <c r="B56" t="s">
+        <v>448</v>
+      </c>
+      <c r="C56" t="s">
+        <v>187</v>
+      </c>
+      <c r="D56" t="s">
+        <v>188</v>
+      </c>
+      <c r="E56" t="s">
+        <v>449</v>
+      </c>
+      <c r="F56" t="s">
+        <v>450</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>452</v>
+      </c>
+      <c r="B57" t="s">
+        <v>453</v>
+      </c>
+      <c r="C57" t="s">
+        <v>181</v>
+      </c>
+      <c r="D57" t="s">
+        <v>188</v>
+      </c>
+      <c r="E57" t="s">
+        <v>454</v>
+      </c>
+      <c r="F57" t="s">
+        <v>455</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>457</v>
+      </c>
+      <c r="B58" t="s">
+        <v>458</v>
+      </c>
+      <c r="C58" t="s">
+        <v>459</v>
+      </c>
+      <c r="D58" t="s">
+        <v>175</v>
+      </c>
+      <c r="E58" t="s">
+        <v>460</v>
+      </c>
+      <c r="F58" t="s">
+        <v>461</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>463</v>
+      </c>
+      <c r="B59" t="s">
+        <v>464</v>
+      </c>
+      <c r="C59" t="s">
+        <v>465</v>
+      </c>
+      <c r="D59" t="s">
+        <v>188</v>
+      </c>
+      <c r="E59" t="s">
+        <v>265</v>
+      </c>
+      <c r="F59" t="s">
+        <v>466</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>468</v>
+      </c>
+      <c r="B60" t="s">
+        <v>464</v>
+      </c>
+      <c r="C60" t="s">
+        <v>465</v>
+      </c>
+      <c r="D60" t="s">
+        <v>188</v>
+      </c>
+      <c r="E60" t="s">
+        <v>265</v>
+      </c>
+      <c r="F60" t="s">
+        <v>466</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>470</v>
+      </c>
+      <c r="B61" t="s">
+        <v>471</v>
+      </c>
+      <c r="C61" t="s">
+        <v>465</v>
+      </c>
+      <c r="D61" t="s">
+        <v>175</v>
+      </c>
+      <c r="E61" t="s">
+        <v>400</v>
+      </c>
+      <c r="F61" t="s">
+        <v>472</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>474</v>
+      </c>
+      <c r="B62" t="s">
+        <v>475</v>
+      </c>
+      <c r="C62" t="s">
+        <v>476</v>
+      </c>
+      <c r="D62" t="s">
+        <v>188</v>
+      </c>
+      <c r="E62" t="s">
+        <v>477</v>
+      </c>
+      <c r="F62" t="s">
+        <v>478</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>480</v>
+      </c>
+      <c r="B63" t="s">
+        <v>481</v>
+      </c>
+      <c r="C63" t="s">
+        <v>181</v>
+      </c>
+      <c r="D63" t="s">
+        <v>188</v>
+      </c>
+      <c r="E63" t="s">
+        <v>482</v>
+      </c>
+      <c r="F63" t="s">
+        <v>250</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>484</v>
+      </c>
+      <c r="B64" t="s">
+        <v>485</v>
+      </c>
+      <c r="C64" t="s">
+        <v>486</v>
+      </c>
+      <c r="D64" t="s">
+        <v>188</v>
+      </c>
+      <c r="E64" t="s">
+        <v>201</v>
+      </c>
+      <c r="F64" t="s">
+        <v>487</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>489</v>
+      </c>
+      <c r="B65" t="s">
+        <v>253</v>
+      </c>
+      <c r="C65" t="s">
+        <v>254</v>
+      </c>
+      <c r="D65" t="s">
+        <v>188</v>
+      </c>
+      <c r="E65" t="s">
+        <v>255</v>
+      </c>
+      <c r="F65" t="s">
+        <v>256</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>491</v>
+      </c>
+      <c r="B66" t="s">
+        <v>492</v>
+      </c>
+      <c r="C66" t="s">
+        <v>187</v>
+      </c>
+      <c r="D66" t="s">
+        <v>399</v>
+      </c>
+      <c r="E66" t="s">
+        <v>493</v>
+      </c>
+      <c r="F66" t="s">
+        <v>494</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>496</v>
+      </c>
+      <c r="B67" t="s">
+        <v>230</v>
+      </c>
+      <c r="C67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D67" t="s">
+        <v>188</v>
+      </c>
+      <c r="E67" t="s">
+        <v>497</v>
+      </c>
+      <c r="F67" t="s">
+        <v>322</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>499</v>
+      </c>
+      <c r="B68" t="s">
+        <v>500</v>
+      </c>
+      <c r="C68" t="s">
+        <v>360</v>
+      </c>
+      <c r="D68" t="s">
+        <v>188</v>
+      </c>
+      <c r="E68" t="s">
+        <v>200</v>
+      </c>
+      <c r="F68" t="s">
+        <v>501</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>503</v>
+      </c>
+      <c r="B69" t="s">
+        <v>504</v>
+      </c>
+      <c r="C69" t="s">
+        <v>181</v>
+      </c>
+      <c r="D69" t="s">
+        <v>188</v>
+      </c>
+      <c r="E69" t="s">
+        <v>505</v>
+      </c>
+      <c r="F69" t="s">
+        <v>506</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>508</v>
+      </c>
+      <c r="B70" t="s">
+        <v>509</v>
+      </c>
+      <c r="C70" t="s">
+        <v>510</v>
+      </c>
+      <c r="D70" t="s">
+        <v>188</v>
+      </c>
+      <c r="E70" t="s">
+        <v>245</v>
+      </c>
+      <c r="F70" t="s">
+        <v>511</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>513</v>
+      </c>
+      <c r="B71" t="s">
+        <v>514</v>
+      </c>
+      <c r="C71" t="s">
+        <v>515</v>
+      </c>
+      <c r="D71" t="s">
+        <v>188</v>
+      </c>
+      <c r="E71" t="s">
+        <v>516</v>
+      </c>
+      <c r="F71" t="s">
+        <v>455</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>518</v>
+      </c>
+      <c r="B72" t="s">
+        <v>519</v>
+      </c>
+      <c r="C72" t="s">
+        <v>187</v>
+      </c>
+      <c r="D72" t="s">
+        <v>188</v>
+      </c>
+      <c r="E72" t="s">
+        <v>520</v>
+      </c>
+      <c r="F72" t="s">
+        <v>521</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>523</v>
+      </c>
+      <c r="B73" t="s">
+        <v>524</v>
+      </c>
+      <c r="C73" t="s">
+        <v>235</v>
+      </c>
+      <c r="D73" t="s">
+        <v>188</v>
+      </c>
+      <c r="E73" t="s">
+        <v>525</v>
+      </c>
+      <c r="F73" t="s">
+        <v>526</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>528</v>
+      </c>
+      <c r="B74" t="s">
+        <v>529</v>
+      </c>
+      <c r="C74" t="s">
+        <v>530</v>
+      </c>
+      <c r="D74" t="s">
+        <v>188</v>
+      </c>
+      <c r="E74" t="s">
+        <v>531</v>
+      </c>
+      <c r="F74" t="s">
+        <v>532</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>528</v>
+      </c>
+      <c r="B75" t="s">
+        <v>529</v>
+      </c>
+      <c r="C75" t="s">
+        <v>534</v>
+      </c>
+      <c r="D75" t="s">
+        <v>188</v>
+      </c>
+      <c r="E75" t="s">
+        <v>531</v>
+      </c>
+      <c r="F75" t="s">
+        <v>532</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>528</v>
+      </c>
+      <c r="B76" t="s">
+        <v>529</v>
+      </c>
+      <c r="C76" t="s">
+        <v>536</v>
+      </c>
+      <c r="D76" t="s">
+        <v>188</v>
+      </c>
+      <c r="E76" t="s">
+        <v>531</v>
+      </c>
+      <c r="F76" t="s">
+        <v>532</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>538</v>
+      </c>
+      <c r="B77" t="s">
+        <v>539</v>
+      </c>
+      <c r="C77" t="s">
+        <v>181</v>
+      </c>
+      <c r="D77" t="s">
+        <v>175</v>
+      </c>
+      <c r="E77" t="s">
+        <v>540</v>
+      </c>
+      <c r="F77" t="s">
+        <v>541</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>543</v>
+      </c>
+      <c r="B78" t="s">
+        <v>544</v>
+      </c>
+      <c r="C78" t="s">
+        <v>181</v>
+      </c>
+      <c r="D78" t="s">
+        <v>188</v>
+      </c>
+      <c r="E78" t="s">
+        <v>545</v>
+      </c>
+      <c r="F78" t="s">
+        <v>546</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>548</v>
+      </c>
+      <c r="B79" t="s">
+        <v>549</v>
+      </c>
+      <c r="C79" t="s">
+        <v>174</v>
+      </c>
+      <c r="D79" t="s">
+        <v>188</v>
+      </c>
+      <c r="E79" t="s">
+        <v>550</v>
+      </c>
+      <c r="F79" t="s">
+        <v>551</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>553</v>
+      </c>
+      <c r="B80" t="s">
+        <v>554</v>
+      </c>
+      <c r="C80" t="s">
+        <v>536</v>
+      </c>
+      <c r="D80" t="s">
+        <v>188</v>
+      </c>
+      <c r="E80" t="s">
+        <v>555</v>
+      </c>
+      <c r="F80" t="s">
+        <v>556</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>558</v>
+      </c>
+      <c r="B81" t="s">
+        <v>549</v>
+      </c>
+      <c r="C81" t="s">
+        <v>174</v>
+      </c>
+      <c r="D81" t="s">
+        <v>188</v>
+      </c>
+      <c r="E81" t="s">
+        <v>550</v>
+      </c>
+      <c r="F81" t="s">
+        <v>551</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>560</v>
+      </c>
+      <c r="B82" t="s">
+        <v>561</v>
+      </c>
+      <c r="C82" t="s">
+        <v>187</v>
+      </c>
+      <c r="D82" t="s">
+        <v>399</v>
+      </c>
+      <c r="E82" t="s">
+        <v>562</v>
+      </c>
+      <c r="F82" t="s">
+        <v>563</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>565</v>
+      </c>
+      <c r="B83" t="s">
+        <v>566</v>
+      </c>
+      <c r="C83" t="s">
+        <v>235</v>
+      </c>
+      <c r="D83" t="s">
+        <v>188</v>
+      </c>
+      <c r="E83" t="s">
+        <v>567</v>
+      </c>
+      <c r="F83" t="s">
+        <v>568</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>570</v>
+      </c>
+      <c r="B84" t="s">
+        <v>571</v>
+      </c>
+      <c r="C84" t="s">
+        <v>572</v>
+      </c>
+      <c r="D84" t="s">
+        <v>188</v>
+      </c>
+      <c r="E84" t="s">
+        <v>276</v>
+      </c>
+      <c r="F84" t="s">
+        <v>573</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>575</v>
+      </c>
+      <c r="B85" t="s">
+        <v>576</v>
+      </c>
+      <c r="C85" t="s">
+        <v>577</v>
+      </c>
+      <c r="D85" t="s">
+        <v>188</v>
+      </c>
+      <c r="E85" t="s">
+        <v>578</v>
+      </c>
+      <c r="F85" t="s">
+        <v>308</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>580</v>
+      </c>
+      <c r="B86" t="s">
+        <v>581</v>
+      </c>
+      <c r="C86" t="s">
+        <v>582</v>
+      </c>
+      <c r="D86" t="s">
+        <v>188</v>
+      </c>
+      <c r="E86" t="s">
+        <v>201</v>
+      </c>
+      <c r="F86" t="s">
+        <v>583</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-08-31.xlsx
+++ b/docs/xlsx/jobs-2026-08-31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="706">
   <si>
     <t>Title</t>
   </si>
@@ -625,6 +625,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/bc0635cd51b3414594cf421e727c519f-assistant-director-of-individual-giving-and-events-university-settlement-society-of-new-york-new-york</t>
   </si>
   <si>
+    <t>Assistant Vice President of Corporate Relations</t>
+  </si>
+  <si>
+    <t>National Association of Student Personnel Administrators</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/379a78fa25b74ca0a8e9589bd55cb39c-assistant-vice-president-of-corporate-relations-national-association-of-student-personnel-administrators-washington</t>
+  </si>
+  <si>
     <t>Attorney - Program Counsel (Michigan Based)</t>
   </si>
   <si>
@@ -670,6 +682,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/9b04b1ffc8b9400f934d850d0841511c-california-senior-finance-director-working-families-kings-county</t>
   </si>
   <si>
+    <t>Campaign Organizer - Denver</t>
+  </si>
+  <si>
+    <t>The Redress Movement</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9fc2426135ff4235a4eac80b04b1005c-campaign-organizer-denver-the-redress-movement-washington</t>
+  </si>
+  <si>
     <t>Case Manager, HomeStart Program</t>
   </si>
   <si>
@@ -721,9 +751,6 @@
     <t>SOME (So Others Might Eat)</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 168376.00 - 178289.28/year</t>
   </si>
   <si>
@@ -733,6 +760,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/29e006b18ace44ff9b11b5ceb5c6c9dd-chief-housing-development-officer-some-so-others-might-eat-washington</t>
   </si>
   <si>
+    <t>Client Service Coordinator</t>
+  </si>
+  <si>
+    <t>Sin Barreras Without Barriers</t>
+  </si>
+  <si>
+    <t>Charlottesville, Virginia</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ed69b7f00914bfea4fb9fbd85152f95-client-service-coordinator-sin-barreras-without-barriers-charlottesville</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30e680a54db240c992b53fa23db2bdbb-client-service-coordinator-sin-barreras-without-barriers-charlottesville</t>
+  </si>
+  <si>
     <t>Clinic Coordinator</t>
   </si>
   <si>
@@ -865,6 +913,21 @@
     <t>https://www.idealist.org/en/job/d3f2160f6feb4f27b703623ae5246e3c-core-scheduling-coordinator-remote-area-medical-rockford</t>
   </si>
   <si>
+    <t>Counsel</t>
+  </si>
+  <si>
+    <t>Legal Advocates for Safe Science and Technology</t>
+  </si>
+  <si>
+    <t>USD 190000.00 - 210000.00/year</t>
+  </si>
+  <si>
+    <t>Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60213314f44e4582b8704ce563e0c85a-counsel-legal-advocates-for-safe-science-and-technology-new-york</t>
+  </si>
+  <si>
     <t>Country Manager, US</t>
   </si>
   <si>
@@ -883,6 +946,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b77e8c223e2e4d1db68b8ce04751d3e3-country-manager-us-350org-washington</t>
   </si>
   <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Climate Science Alliance</t>
+  </si>
+  <si>
+    <t>San Diego, California</t>
+  </si>
+  <si>
+    <t>USD 43.00 - 48.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35bf567d36684f9b8beb362b732c8778-development-director-climate-science-alliance-san-diego</t>
+  </si>
+  <si>
     <t>Development Manager</t>
   </si>
   <si>
@@ -901,6 +982,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/3131f646135445c997bfa25b1925c9aa-development-manager-kates-club-brookhaven</t>
   </si>
   <si>
+    <t>Director of Administration and Finance</t>
+  </si>
+  <si>
+    <t>Weeksville Heritage Center</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e91202a43d3c43bf8742e21cd60cf033-director-of-administration-and-finance-weeksville-heritage-center-kings-county</t>
+  </si>
+  <si>
+    <t>Director of Communications</t>
+  </si>
+  <si>
+    <t>Verité</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fb36069b90a465a9f78d623d267bffc-director-of-communications-verite-amherst</t>
+  </si>
+  <si>
     <t>Director of Corporate and Foundation Relations</t>
   </si>
   <si>
@@ -958,6 +1066,36 @@
     <t>https://www.idealist.org/en/job/874a04dc3fd140d894b4799afd3f689a-director-of-development-converge-partners-in-access-ridgeland</t>
   </si>
   <si>
+    <t>Carr Assessments</t>
+  </si>
+  <si>
+    <t>Remote (Sacramento, California)</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/97ad8542fa7e4dd1bceb517732b6588e-director-of-development-carr-assessments-sacramento</t>
+  </si>
+  <si>
+    <t>Love146, New Haven, CT</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26b96fcebbdd4d14bbc2ac8aea5a32ed-director-of-development-love146-new-haven-ct-new-haven</t>
+  </si>
+  <si>
     <t>Director of People &amp; Operations</t>
   </si>
   <si>
@@ -1072,6 +1210,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/61233e240d544361b1a3c8b284dc9d5e-entry-level-attorney-criminal-defense-practice-september-2027-queens-office-brooklyn-defender-services-queens-county</t>
   </si>
   <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>Beth David Reform Congregation</t>
+  </si>
+  <si>
+    <t>Lower Merion Township, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Religion Spirituality, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b490d9ce62443e39fb638c2aa0dc977-executive-assistant-beth-david-reform-congregation-lower-merion-township</t>
+  </si>
+  <si>
     <t>Executive Associate</t>
   </si>
   <si>
@@ -1225,6 +1381,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/128a3401fb53472597ca78180ce8edd9-freelance-online-event-host-70-faces-media-new-york</t>
   </si>
   <si>
+    <t>Grant Administrator - Chemistry</t>
+  </si>
+  <si>
+    <t>New York University</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 93019.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/d2cd6f91f98841bd843ec184b35e43da-grant-administrator-chemistry-new-york-university-new-york</t>
+  </si>
+  <si>
     <t>Grants &amp; Operations Manager</t>
   </si>
   <si>
@@ -1258,6 +1426,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/752ef1be8f0148fb94776429430c1486-grants-and-development-manager-formerly-incarcerated-convicted-people-families-movement-ficpfm-windermere</t>
   </si>
   <si>
+    <t>Graphic Designer, Girls on the Run Headquarters</t>
+  </si>
+  <si>
+    <t>Girls on the Run International</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 25.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e05de7b36c44627a5cf5b1e33bb1967-graphic-designer-girls-on-the-run-headquarters-girls-on-the-run-international-charlotte</t>
+  </si>
+  <si>
+    <t>Head of Litigation</t>
+  </si>
+  <si>
+    <t>USD 280000.00 - 295000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec0e1c63cb3f44d88875d255a1a80341-head-of-litigation-legal-advocates-for-safe-science-and-technology-new-york</t>
+  </si>
+  <si>
     <t>Health Education Program Coordinator – YMSM Program</t>
   </si>
   <si>
@@ -1291,6 +1483,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/0c073361610b4d5bac7efb3b892d7e6f-hud-certified-foreclosure-prevention-housing-counselor-housing-help-inc-east-northport</t>
   </si>
   <si>
+    <t>Human Resources Assistant</t>
+  </si>
+  <si>
+    <t>Legacy LA Youth Development Corporation</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e18a998822df4e5a8b2522896e979c55-human-resources-assistant-legacy-la-youth-development-corporation-los-angeles</t>
+  </si>
+  <si>
     <t>Individual Gifts Officer</t>
   </si>
   <si>
@@ -1351,9 +1561,6 @@
     <t>USD 95000.00 - 110000.00/year</t>
   </si>
   <si>
-    <t>Job Workplace</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/55eb4c5da55f47438184ce1f44a7090d-leadership-gift-officer-graduate-school-of-journalism-columbia-university-hr-new-york</t>
   </si>
   <si>
@@ -1372,6 +1579,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/411f2f6fa6c44863bff90d08b9f0c7ac-major-gifts-officer-codeai-seattle</t>
   </si>
   <si>
+    <t>Mobility Mentoring Coach</t>
+  </si>
+  <si>
+    <t>University District Food Bank</t>
+  </si>
+  <si>
+    <t>USD 38.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/15fd9cb38bad42a3ae84703b8bd14f4c-mobility-mentoring-coach-university-district-food-bank-seattle</t>
+  </si>
+  <si>
+    <t>Music Clubhouse Specialist</t>
+  </si>
+  <si>
+    <t>West End House</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7d3887da71b4788b2884cf73c384322-music-clubhouse-specialist-west-end-house-boston</t>
+  </si>
+  <si>
+    <t>Nonprofit Senior Accountant (Full Time, Remote)</t>
+  </si>
+  <si>
+    <t>JFW Accounting Services LLC CPA</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/eaa08a51ae484bffa83ef13faf850b77-nonprofit-senior-accountant-full-time-remote-jfw-accounting-services-llc-cpa-washington</t>
+  </si>
+  <si>
     <t>Operations and Finance Administration Manager</t>
   </si>
   <si>
@@ -1411,9 +1657,6 @@
     <t>BRIC</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
     <t>Arts Music, Education, Media</t>
   </si>
   <si>
@@ -1426,6 +1669,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/8d70377dee6d4454995b68d9a6bfc66e-operations-manager-facilities-building-management-bric-kings-county</t>
   </si>
   <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Immigrant Advocacy Network</t>
+  </si>
+  <si>
+    <t>Westminster, Colorado</t>
+  </si>
+  <si>
+    <t>USD 53000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fbc13f8ac5ed47a5a66e013691cd9cc9-paralegal-rocky-mountain-immigrant-advocacy-network-westminster</t>
+  </si>
+  <si>
     <t>Part-Time Youth Instructor — No Boatbuilding Experience Required</t>
   </si>
   <si>
@@ -1462,9 +1723,6 @@
     <t>Youth Justice Network</t>
   </si>
   <si>
-    <t>USD 45000.00 - 50000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/da78c580d556437eb9be6864bcb5af5d-peer-specialist-youth-justice-network-new-york</t>
   </si>
   <si>
@@ -1483,6 +1741,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/3d52e6cd9ecf48daaf0d1426ffc6fceb-pessoa-assessora-administrativa-financeira-i-instituto-de-defesa-do-direito-de-defesa-marcio-thomaz-bastos-sao-paulo</t>
   </si>
   <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>FLIPANY</t>
+  </si>
+  <si>
+    <t>Deerfield Beach, Florida</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98f5d93fa59740289967f58d1c18f256-program-manager-flipany-deerfield-beach</t>
+  </si>
+  <si>
     <t>Programs Manager</t>
   </si>
   <si>
@@ -1504,6 +1780,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/7e4409e7968a4f1cb3719b2f61d4a07c-project-coordinator-k-12-career-navigation-system-qa-commons-st-helena</t>
   </si>
   <si>
+    <t>Remote Development Associate Consultant</t>
+  </si>
+  <si>
+    <t>A. Marie Consultants</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/6132026828aa46d48ffbd13e41e29ee5-remote-development-associate-consultant-a-marie-consultants-greater-landover</t>
+  </si>
+  <si>
     <t>Senior Accountant / Operations Specialist</t>
   </si>
   <si>
@@ -1540,6 +1828,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/a6f5706812394133baf21b67c7637c5e-senior-campaign-organizer-association-for-neighborhood-and-housing-development-new-york</t>
   </si>
   <si>
+    <t>Senior Communications Manager</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b5b69661b1342faabb71bdf9cf5090f-senior-communications-manager-climate-science-alliance-san-diego</t>
+  </si>
+  <si>
     <t>Senior Development Manager</t>
   </si>
   <si>
@@ -1585,6 +1885,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/a57d3f82c87a4c068245b5562079b5e0-senior-manager-nonprofit-member-experience-good360-alexandria</t>
   </si>
   <si>
+    <t>Senior Media Relations Manager</t>
+  </si>
+  <si>
+    <t>Way to Win</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a11b462ff8f5454ab25946fe5126b78a-senior-media-relations-manager-way-to-win-washington</t>
+  </si>
+  <si>
     <t>Senior Policy Advisor</t>
   </si>
   <si>
@@ -1612,9 +1921,6 @@
     <t>USD 125000.00 - 140000.00/year</t>
   </si>
   <si>
-    <t>Immigrants Or Refugees, Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/27f92264bec34cc9908b94a78456e7de-senior-project-manager-immigrant-legal-resource-center-fresno</t>
   </si>
   <si>
@@ -1630,6 +1936,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/9ad52abddd0e4d20a2275eef34bda964-senior-project-manager-immigrant-legal-resource-center-san-francisco</t>
   </si>
   <si>
+    <t>Shop Manager</t>
+  </si>
+  <si>
+    <t>The Junior League of Palo Alto Mid Peninsula</t>
+  </si>
+  <si>
+    <t>Menlo Park, California</t>
+  </si>
+  <si>
+    <t>Education, Hunger Food Security, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3a101017c8140008041919e3c6c4748-shop-manager-the-junior-league-of-palo-alto-mid-peninsula-menlo-park</t>
+  </si>
+  <si>
     <t>Social Media Coordinator</t>
   </si>
   <si>
@@ -1645,6 +1966,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/b214686fa92542a294cfc618bfee4138-social-media-coordinator-the-cathedral-church-of-saint-john-the-divine-of-new-york-new-york</t>
   </si>
   <si>
+    <t>Southeast Region Lands Project Manager</t>
+  </si>
+  <si>
+    <t>American Battlefield Trust</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a2b9a9d286524ec9baf3808a9f8ca1ac-southeast-region-lands-project-manager-american-battlefield-trust-washington</t>
+  </si>
+  <si>
+    <t>Special Assistant to Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7637bac45c7c43a5967fbfff45286e5b-special-assistant-to-chief-executive-officer-the-choice-inc-washington</t>
+  </si>
+  <si>
     <t>Staff Attorney</t>
   </si>
   <si>
@@ -1720,10 +2071,22 @@
     <t>USD 2000.00 - 2000.00/month</t>
   </si>
   <si>
-    <t>Children Youth, Civic Engagement, Community Development</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/c174e828ef11477c8accf7c9462784c3-student-and-family-engagement-service-member-kid-power-inc-washington</t>
+  </si>
+  <si>
+    <t>Trip Assistant - Chiang Mai</t>
+  </si>
+  <si>
+    <t>Global Public Service Academies</t>
+  </si>
+  <si>
+    <t>Chiang Mai, Chiang Mai, TH</t>
+  </si>
+  <si>
+    <t>THB 2000.00 - 3000.00/day</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b15f38f551e4169b5c7fd07d9ae8393-trip-assistant-chiang-mai-global-public-service-academies-chiang-mai</t>
   </si>
   <si>
     <t>Vice President of Finance and Operations</t>
@@ -2996,7 +3359,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3158,36 +3521,36 @@
         <v>204</v>
       </c>
       <c r="C7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" t="s">
         <v>205</v>
       </c>
-      <c r="D7" t="s">
-        <v>188</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="F7" t="s">
-        <v>207</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" t="s">
         <v>209</v>
       </c>
-      <c r="B8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" t="s">
         <v>210</v>
-      </c>
-      <c r="D8" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" t="s">
-        <v>206</v>
       </c>
       <c r="F8" t="s">
         <v>211</v>
@@ -3201,79 +3564,79 @@
         <v>213</v>
       </c>
       <c r="B9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" t="s">
         <v>214</v>
       </c>
-      <c r="C9" t="s">
-        <v>187</v>
-      </c>
       <c r="D9" t="s">
         <v>188</v>
       </c>
       <c r="E9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F9" t="s">
         <v>215</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" t="s">
         <v>218</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" t="s">
         <v>219</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>220</v>
       </c>
-      <c r="D10" t="s">
-        <v>188</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="H10" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F10" t="s">
-        <v>222</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" t="s">
         <v>224</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" t="s">
         <v>225</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>226</v>
       </c>
-      <c r="D11" t="s">
-        <v>188</v>
-      </c>
-      <c r="E11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="H11" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" t="s">
         <v>229</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>230</v>
-      </c>
-      <c r="C12" t="s">
-        <v>187</v>
       </c>
       <c r="D12" t="s">
         <v>188</v>
@@ -3282,27 +3645,27 @@
         <v>231</v>
       </c>
       <c r="F12" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D13" t="s">
         <v>188</v>
       </c>
       <c r="E13" t="s">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="F13" t="s">
         <v>237</v>
@@ -3319,13 +3682,13 @@
         <v>240</v>
       </c>
       <c r="C14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" t="s">
         <v>241</v>
-      </c>
-      <c r="D14" t="s">
-        <v>188</v>
-      </c>
-      <c r="E14" t="s">
-        <v>201</v>
       </c>
       <c r="F14" t="s">
         <v>201</v>
@@ -3342,7 +3705,7 @@
         <v>244</v>
       </c>
       <c r="C15" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="D15" t="s">
         <v>188</v>
@@ -3359,220 +3722,220 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s">
         <v>188</v>
       </c>
       <c r="E16" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>248</v>
+      </c>
+      <c r="B17" t="s">
+        <v>249</v>
+      </c>
+      <c r="C17" t="s">
+        <v>250</v>
+      </c>
+      <c r="D17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F17" t="s">
         <v>252</v>
       </c>
-      <c r="B17" t="s">
-        <v>253</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="H17" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="D17" t="s">
-        <v>188</v>
-      </c>
-      <c r="E17" t="s">
-        <v>255</v>
-      </c>
-      <c r="F17" t="s">
-        <v>256</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B18" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C18" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="D18" t="s">
         <v>188</v>
       </c>
       <c r="E18" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="F18" t="s">
         <v>201</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>259</v>
+      </c>
+      <c r="B19" t="s">
+        <v>260</v>
+      </c>
+      <c r="C19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" t="s">
+        <v>261</v>
+      </c>
+      <c r="F19" t="s">
         <v>262</v>
       </c>
-      <c r="B19" t="s">
+      <c r="H19" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="C19" t="s">
-        <v>264</v>
-      </c>
-      <c r="D19" t="s">
-        <v>188</v>
-      </c>
-      <c r="E19" t="s">
-        <v>265</v>
-      </c>
-      <c r="F19" t="s">
-        <v>266</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B20" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C20" t="s">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
         <v>188</v>
       </c>
       <c r="E20" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F20" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B21" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C21" t="s">
-        <v>187</v>
+        <v>270</v>
       </c>
       <c r="D21" t="s">
         <v>188</v>
       </c>
       <c r="E21" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F21" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B22" t="s">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="C22" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D22" t="s">
         <v>188</v>
       </c>
       <c r="E22" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" t="s">
         <v>201</v>
       </c>
-      <c r="F22" t="s">
-        <v>227</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>278</v>
+      </c>
+      <c r="B23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" t="s">
+        <v>280</v>
+      </c>
+      <c r="D23" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" t="s">
         <v>281</v>
       </c>
-      <c r="B23" t="s">
-        <v>240</v>
-      </c>
-      <c r="C23" t="s">
-        <v>241</v>
-      </c>
-      <c r="D23" t="s">
-        <v>188</v>
-      </c>
-      <c r="E23" t="s">
-        <v>201</v>
-      </c>
       <c r="F23" t="s">
-        <v>201</v>
+        <v>282</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C24" t="s">
-        <v>187</v>
+        <v>286</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>188</v>
       </c>
       <c r="E24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B25" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C25" t="s">
-        <v>291</v>
+        <v>187</v>
       </c>
       <c r="D25" t="s">
         <v>188</v>
@@ -3592,33 +3955,33 @@
         <v>295</v>
       </c>
       <c r="B26" t="s">
+        <v>235</v>
+      </c>
+      <c r="C26" t="s">
+        <v>236</v>
+      </c>
+      <c r="D26" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" t="s">
+        <v>201</v>
+      </c>
+      <c r="F26" t="s">
+        <v>237</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="C26" t="s">
-        <v>235</v>
-      </c>
-      <c r="D26" t="s">
-        <v>188</v>
-      </c>
-      <c r="E26" t="s">
-        <v>297</v>
-      </c>
-      <c r="F26" t="s">
-        <v>298</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s">
-        <v>301</v>
+        <v>256</v>
       </c>
       <c r="C27" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="D27" t="s">
         <v>188</v>
@@ -3627,918 +3990,918 @@
         <v>201</v>
       </c>
       <c r="F27" t="s">
-        <v>303</v>
+        <v>201</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>299</v>
+      </c>
+      <c r="B28" t="s">
         <v>300</v>
       </c>
-      <c r="B28" t="s">
-        <v>305</v>
-      </c>
       <c r="C28" t="s">
-        <v>306</v>
+        <v>187</v>
       </c>
       <c r="D28" t="s">
         <v>188</v>
       </c>
       <c r="E28" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="F28" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C29" t="s">
         <v>187</v>
       </c>
       <c r="D29" t="s">
-        <v>188</v>
+        <v>306</v>
       </c>
       <c r="E29" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F29" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B30" t="s">
+        <v>311</v>
+      </c>
+      <c r="C30" t="s">
+        <v>312</v>
+      </c>
+      <c r="D30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" t="s">
+        <v>313</v>
+      </c>
+      <c r="F30" t="s">
         <v>314</v>
       </c>
-      <c r="B30" t="s">
+      <c r="H30" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="C30" t="s">
-        <v>235</v>
-      </c>
-      <c r="D30" t="s">
-        <v>188</v>
-      </c>
-      <c r="E30" t="s">
-        <v>316</v>
-      </c>
-      <c r="F30" t="s">
-        <v>317</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>316</v>
+      </c>
+      <c r="B31" t="s">
+        <v>317</v>
+      </c>
+      <c r="C31" t="s">
+        <v>318</v>
+      </c>
+      <c r="D31" t="s">
+        <v>188</v>
+      </c>
+      <c r="E31" t="s">
         <v>319</v>
       </c>
-      <c r="B31" t="s">
+      <c r="F31" t="s">
         <v>320</v>
       </c>
-      <c r="C31" t="s">
-        <v>181</v>
-      </c>
-      <c r="D31" t="s">
-        <v>285</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="H31" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="F31" t="s">
-        <v>322</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>322</v>
+      </c>
+      <c r="B32" t="s">
+        <v>323</v>
+      </c>
+      <c r="C32" t="s">
         <v>324</v>
       </c>
-      <c r="B32" t="s">
-        <v>325</v>
-      </c>
-      <c r="C32" t="s">
-        <v>235</v>
-      </c>
       <c r="D32" t="s">
         <v>188</v>
       </c>
       <c r="E32" t="s">
-        <v>326</v>
+        <v>292</v>
       </c>
       <c r="F32" t="s">
         <v>201</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B33" t="s">
+        <v>327</v>
+      </c>
+      <c r="C33" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" t="s">
         <v>328</v>
       </c>
-      <c r="B33" t="s">
+      <c r="F33" t="s">
         <v>329</v>
       </c>
-      <c r="C33" t="s">
+      <c r="H33" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="D33" t="s">
-        <v>188</v>
-      </c>
-      <c r="E33" t="s">
-        <v>331</v>
-      </c>
-      <c r="F33" t="s">
-        <v>332</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>331</v>
+      </c>
+      <c r="B34" t="s">
+        <v>332</v>
+      </c>
+      <c r="C34" t="s">
+        <v>224</v>
+      </c>
+      <c r="D34" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" t="s">
+        <v>333</v>
+      </c>
+      <c r="F34" t="s">
         <v>334</v>
       </c>
-      <c r="B34" t="s">
+      <c r="H34" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="C34" t="s">
-        <v>336</v>
-      </c>
-      <c r="D34" t="s">
-        <v>188</v>
-      </c>
-      <c r="E34" t="s">
-        <v>337</v>
-      </c>
-      <c r="F34" t="s">
-        <v>338</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>336</v>
+      </c>
+      <c r="B35" t="s">
+        <v>337</v>
+      </c>
+      <c r="C35" t="s">
+        <v>338</v>
+      </c>
+      <c r="D35" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" t="s">
+        <v>201</v>
+      </c>
+      <c r="F35" t="s">
+        <v>339</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="B35" t="s">
-        <v>341</v>
-      </c>
-      <c r="C35" t="s">
-        <v>342</v>
-      </c>
-      <c r="D35" t="s">
-        <v>188</v>
-      </c>
-      <c r="E35" t="s">
-        <v>343</v>
-      </c>
-      <c r="F35" t="s">
-        <v>344</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="C36" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D36" t="s">
         <v>188</v>
       </c>
       <c r="E36" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="F36" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="C37" t="s">
-        <v>330</v>
+        <v>187</v>
       </c>
       <c r="D37" t="s">
         <v>188</v>
       </c>
       <c r="E37" t="s">
+        <v>347</v>
+      </c>
+      <c r="F37" t="s">
         <v>348</v>
       </c>
-      <c r="F37" t="s">
-        <v>332</v>
-      </c>
       <c r="H37" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>336</v>
+      </c>
+      <c r="B38" t="s">
+        <v>350</v>
+      </c>
+      <c r="C38" t="s">
+        <v>351</v>
+      </c>
+      <c r="D38" t="s">
+        <v>188</v>
+      </c>
+      <c r="E38" t="s">
         <v>352</v>
       </c>
-      <c r="B38" t="s">
+      <c r="F38" t="s">
         <v>353</v>
       </c>
-      <c r="C38" t="s">
+      <c r="H38" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="D38" t="s">
-        <v>188</v>
-      </c>
-      <c r="E38" t="s">
-        <v>355</v>
-      </c>
-      <c r="F38" t="s">
-        <v>356</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>336</v>
+      </c>
+      <c r="B39" t="s">
+        <v>355</v>
+      </c>
+      <c r="C39" t="s">
+        <v>356</v>
+      </c>
+      <c r="D39" t="s">
+        <v>188</v>
+      </c>
+      <c r="E39" t="s">
+        <v>357</v>
+      </c>
+      <c r="F39" t="s">
         <v>358</v>
       </c>
-      <c r="B39" t="s">
+      <c r="H39" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="C39" t="s">
-        <v>360</v>
-      </c>
-      <c r="D39" t="s">
-        <v>188</v>
-      </c>
-      <c r="E39" t="s">
-        <v>361</v>
-      </c>
-      <c r="F39" t="s">
-        <v>362</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B40" t="s">
+        <v>361</v>
+      </c>
+      <c r="C40" t="s">
+        <v>224</v>
+      </c>
+      <c r="D40" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" t="s">
+        <v>362</v>
+      </c>
+      <c r="F40" t="s">
+        <v>363</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="C40" t="s">
-        <v>365</v>
-      </c>
-      <c r="D40" t="s">
-        <v>188</v>
-      </c>
-      <c r="E40" t="s">
-        <v>366</v>
-      </c>
-      <c r="F40" t="s">
-        <v>367</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s">
+        <v>366</v>
+      </c>
+      <c r="C41" t="s">
+        <v>181</v>
+      </c>
+      <c r="D41" t="s">
+        <v>306</v>
+      </c>
+      <c r="E41" t="s">
+        <v>367</v>
+      </c>
+      <c r="F41" t="s">
+        <v>368</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="C41" t="s">
-        <v>370</v>
-      </c>
-      <c r="D41" t="s">
-        <v>188</v>
-      </c>
-      <c r="E41" t="s">
-        <v>371</v>
-      </c>
-      <c r="F41" t="s">
-        <v>372</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B42" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C42" t="s">
-        <v>375</v>
+        <v>224</v>
       </c>
       <c r="D42" t="s">
         <v>188</v>
       </c>
       <c r="E42" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F42" t="s">
-        <v>377</v>
+        <v>201</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="B43" t="s">
+        <v>375</v>
+      </c>
+      <c r="C43" t="s">
+        <v>376</v>
+      </c>
+      <c r="D43" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43" t="s">
+        <v>377</v>
+      </c>
+      <c r="F43" t="s">
+        <v>378</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="C43" t="s">
-        <v>380</v>
-      </c>
-      <c r="D43" t="s">
-        <v>188</v>
-      </c>
-      <c r="E43" t="s">
-        <v>381</v>
-      </c>
-      <c r="F43" t="s">
-        <v>382</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s">
+        <v>381</v>
+      </c>
+      <c r="C44" t="s">
+        <v>382</v>
+      </c>
+      <c r="D44" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" t="s">
+        <v>383</v>
+      </c>
+      <c r="F44" t="s">
         <v>384</v>
       </c>
-      <c r="C44" t="s">
+      <c r="H44" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="D44" t="s">
-        <v>188</v>
-      </c>
-      <c r="E44" t="s">
-        <v>386</v>
-      </c>
-      <c r="F44" t="s">
-        <v>387</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="B45" t="s">
+        <v>387</v>
+      </c>
+      <c r="C45" t="s">
+        <v>388</v>
+      </c>
+      <c r="D45" t="s">
+        <v>188</v>
+      </c>
+      <c r="E45" t="s">
         <v>389</v>
       </c>
-      <c r="C45" t="s">
+      <c r="F45" t="s">
         <v>390</v>
       </c>
-      <c r="D45" t="s">
-        <v>188</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="H45" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="F45" t="s">
-        <v>308</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>392</v>
+      </c>
+      <c r="B46" t="s">
+        <v>375</v>
+      </c>
+      <c r="C46" t="s">
         <v>393</v>
       </c>
-      <c r="B46" t="s">
-        <v>335</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
+        <v>188</v>
+      </c>
+      <c r="E46" t="s">
         <v>394</v>
       </c>
-      <c r="D46" t="s">
-        <v>188</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
+        <v>378</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="F46" t="s">
-        <v>338</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>396</v>
+      </c>
+      <c r="B47" t="s">
+        <v>375</v>
+      </c>
+      <c r="C47" t="s">
+        <v>376</v>
+      </c>
+      <c r="D47" t="s">
+        <v>188</v>
+      </c>
+      <c r="E47" t="s">
+        <v>394</v>
+      </c>
+      <c r="F47" t="s">
+        <v>378</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="B47" t="s">
-        <v>398</v>
-      </c>
-      <c r="C47" t="s">
-        <v>187</v>
-      </c>
-      <c r="D47" t="s">
-        <v>399</v>
-      </c>
-      <c r="E47" t="s">
-        <v>400</v>
-      </c>
-      <c r="F47" t="s">
-        <v>401</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>398</v>
+      </c>
+      <c r="B48" t="s">
+        <v>399</v>
+      </c>
+      <c r="C48" t="s">
+        <v>400</v>
+      </c>
+      <c r="D48" t="s">
+        <v>188</v>
+      </c>
+      <c r="E48" t="s">
+        <v>401</v>
+      </c>
+      <c r="F48" t="s">
+        <v>402</v>
+      </c>
+      <c r="H48" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="B48" t="s">
-        <v>404</v>
-      </c>
-      <c r="C48" t="s">
-        <v>405</v>
-      </c>
-      <c r="D48" t="s">
-        <v>188</v>
-      </c>
-      <c r="E48" t="s">
-        <v>406</v>
-      </c>
-      <c r="F48" t="s">
-        <v>407</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>404</v>
+      </c>
+      <c r="B49" t="s">
+        <v>405</v>
+      </c>
+      <c r="C49" t="s">
+        <v>406</v>
+      </c>
+      <c r="D49" t="s">
+        <v>188</v>
+      </c>
+      <c r="E49" t="s">
+        <v>407</v>
+      </c>
+      <c r="F49" t="s">
+        <v>408</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="B49" t="s">
-        <v>410</v>
-      </c>
-      <c r="C49" t="s">
-        <v>187</v>
-      </c>
-      <c r="D49" t="s">
-        <v>188</v>
-      </c>
-      <c r="E49" t="s">
-        <v>411</v>
-      </c>
-      <c r="F49" t="s">
-        <v>412</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>410</v>
+      </c>
+      <c r="B50" t="s">
+        <v>411</v>
+      </c>
+      <c r="C50" t="s">
+        <v>412</v>
+      </c>
+      <c r="D50" t="s">
+        <v>188</v>
+      </c>
+      <c r="E50" t="s">
+        <v>413</v>
+      </c>
+      <c r="F50" t="s">
         <v>414</v>
       </c>
-      <c r="B50" t="s">
+      <c r="H50" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="C50" t="s">
-        <v>330</v>
-      </c>
-      <c r="D50" t="s">
-        <v>188</v>
-      </c>
-      <c r="E50" t="s">
-        <v>416</v>
-      </c>
-      <c r="F50" t="s">
-        <v>417</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>410</v>
+      </c>
+      <c r="B51" t="s">
+        <v>416</v>
+      </c>
+      <c r="C51" t="s">
+        <v>417</v>
+      </c>
+      <c r="D51" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51" t="s">
+        <v>418</v>
+      </c>
+      <c r="F51" t="s">
         <v>419</v>
       </c>
-      <c r="B51" t="s">
+      <c r="H51" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="C51" t="s">
-        <v>421</v>
-      </c>
-      <c r="D51" t="s">
-        <v>188</v>
-      </c>
-      <c r="E51" t="s">
-        <v>422</v>
-      </c>
-      <c r="F51" t="s">
-        <v>423</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>410</v>
+      </c>
+      <c r="B52" t="s">
+        <v>421</v>
+      </c>
+      <c r="C52" t="s">
+        <v>422</v>
+      </c>
+      <c r="D52" t="s">
+        <v>188</v>
+      </c>
+      <c r="E52" t="s">
+        <v>423</v>
+      </c>
+      <c r="F52" t="s">
+        <v>424</v>
+      </c>
+      <c r="H52" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="B52" t="s">
-        <v>426</v>
-      </c>
-      <c r="C52" t="s">
-        <v>235</v>
-      </c>
-      <c r="D52" t="s">
-        <v>188</v>
-      </c>
-      <c r="E52" t="s">
-        <v>427</v>
-      </c>
-      <c r="F52" t="s">
-        <v>428</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>410</v>
+      </c>
+      <c r="B53" t="s">
+        <v>426</v>
+      </c>
+      <c r="C53" t="s">
+        <v>427</v>
+      </c>
+      <c r="D53" t="s">
+        <v>188</v>
+      </c>
+      <c r="E53" t="s">
+        <v>428</v>
+      </c>
+      <c r="F53" t="s">
+        <v>429</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="B53" t="s">
-        <v>431</v>
-      </c>
-      <c r="C53" t="s">
-        <v>432</v>
-      </c>
-      <c r="D53" t="s">
-        <v>188</v>
-      </c>
-      <c r="E53" t="s">
-        <v>433</v>
-      </c>
-      <c r="F53" t="s">
-        <v>434</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="B54" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C54" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D54" t="s">
         <v>188</v>
       </c>
       <c r="E54" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="F54" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="B55" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="C55" t="s">
-        <v>181</v>
+        <v>437</v>
       </c>
       <c r="D55" t="s">
         <v>188</v>
       </c>
       <c r="E55" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="F55" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>447</v>
+        <v>410</v>
       </c>
       <c r="B56" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="C56" t="s">
-        <v>187</v>
+        <v>442</v>
       </c>
       <c r="D56" t="s">
         <v>188</v>
       </c>
       <c r="E56" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="F56" t="s">
-        <v>450</v>
+        <v>344</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="B57" t="s">
-        <v>453</v>
+        <v>381</v>
       </c>
       <c r="C57" t="s">
-        <v>181</v>
+        <v>446</v>
       </c>
       <c r="D57" t="s">
         <v>188</v>
       </c>
       <c r="E57" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="F57" t="s">
-        <v>455</v>
+        <v>384</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="B58" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C58" t="s">
-        <v>459</v>
+        <v>187</v>
       </c>
       <c r="D58" t="s">
-        <v>175</v>
+        <v>451</v>
       </c>
       <c r="E58" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="F58" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C59" t="s">
-        <v>465</v>
+        <v>181</v>
       </c>
       <c r="D59" t="s">
         <v>188</v>
       </c>
       <c r="E59" t="s">
-        <v>265</v>
+        <v>457</v>
       </c>
       <c r="F59" t="s">
-        <v>466</v>
+        <v>201</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="B60" t="s">
+        <v>460</v>
+      </c>
+      <c r="C60" t="s">
+        <v>461</v>
+      </c>
+      <c r="D60" t="s">
+        <v>188</v>
+      </c>
+      <c r="E60" t="s">
+        <v>462</v>
+      </c>
+      <c r="F60" t="s">
+        <v>463</v>
+      </c>
+      <c r="H60" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="C60" t="s">
-        <v>465</v>
-      </c>
-      <c r="D60" t="s">
-        <v>188</v>
-      </c>
-      <c r="E60" t="s">
-        <v>265</v>
-      </c>
-      <c r="F60" t="s">
-        <v>466</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B61" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C61" t="s">
-        <v>465</v>
+        <v>187</v>
       </c>
       <c r="D61" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="E61" t="s">
-        <v>400</v>
+        <v>467</v>
       </c>
       <c r="F61" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>470</v>
+      </c>
+      <c r="B62" t="s">
+        <v>471</v>
+      </c>
+      <c r="C62" t="s">
+        <v>187</v>
+      </c>
+      <c r="D62" t="s">
+        <v>188</v>
+      </c>
+      <c r="E62" t="s">
+        <v>472</v>
+      </c>
+      <c r="F62" t="s">
+        <v>473</v>
+      </c>
+      <c r="H62" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="B62" t="s">
-        <v>475</v>
-      </c>
-      <c r="C62" t="s">
-        <v>476</v>
-      </c>
-      <c r="D62" t="s">
-        <v>188</v>
-      </c>
-      <c r="E62" t="s">
-        <v>477</v>
-      </c>
-      <c r="F62" t="s">
-        <v>478</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s">
-        <v>481</v>
+        <v>300</v>
       </c>
       <c r="C63" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D63" t="s">
         <v>188</v>
       </c>
       <c r="E63" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="F63" t="s">
-        <v>250</v>
+        <v>302</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B64" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C64" t="s">
-        <v>486</v>
+        <v>376</v>
       </c>
       <c r="D64" t="s">
         <v>188</v>
       </c>
       <c r="E64" t="s">
-        <v>201</v>
+        <v>480</v>
       </c>
       <c r="F64" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B65" t="s">
-        <v>253</v>
+        <v>484</v>
       </c>
       <c r="C65" t="s">
-        <v>254</v>
+        <v>485</v>
       </c>
       <c r="D65" t="s">
         <v>188</v>
       </c>
       <c r="E65" t="s">
-        <v>255</v>
+        <v>486</v>
       </c>
       <c r="F65" t="s">
-        <v>256</v>
+        <v>487</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>489</v>
+      </c>
+      <c r="B66" t="s">
+        <v>490</v>
+      </c>
+      <c r="C66" t="s">
         <v>491</v>
       </c>
-      <c r="B66" t="s">
+      <c r="D66" t="s">
+        <v>188</v>
+      </c>
+      <c r="E66" t="s">
         <v>492</v>
       </c>
-      <c r="C66" t="s">
-        <v>187</v>
-      </c>
-      <c r="D66" t="s">
-        <v>399</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>493</v>
       </c>
-      <c r="F66" t="s">
+      <c r="H66" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>495</v>
+      </c>
+      <c r="B67" t="s">
         <v>496</v>
       </c>
-      <c r="B67" t="s">
-        <v>230</v>
-      </c>
       <c r="C67" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="D67" t="s">
         <v>188</v>
@@ -4547,168 +4910,168 @@
         <v>497</v>
       </c>
       <c r="F67" t="s">
-        <v>322</v>
+        <v>498</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B68" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C68" t="s">
-        <v>360</v>
+        <v>502</v>
       </c>
       <c r="D68" t="s">
         <v>188</v>
       </c>
       <c r="E68" t="s">
-        <v>200</v>
+        <v>503</v>
       </c>
       <c r="F68" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B69" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C69" t="s">
-        <v>181</v>
+        <v>508</v>
       </c>
       <c r="D69" t="s">
         <v>188</v>
       </c>
       <c r="E69" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F69" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B70" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C70" t="s">
-        <v>510</v>
+        <v>181</v>
       </c>
       <c r="D70" t="s">
         <v>188</v>
       </c>
       <c r="E70" t="s">
-        <v>245</v>
+        <v>514</v>
       </c>
       <c r="F70" t="s">
-        <v>511</v>
+        <v>353</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B71" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C71" t="s">
-        <v>515</v>
+        <v>187</v>
       </c>
       <c r="D71" t="s">
         <v>188</v>
       </c>
       <c r="E71" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F71" t="s">
-        <v>455</v>
+        <v>519</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B72" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C72" t="s">
-        <v>187</v>
+        <v>42</v>
       </c>
       <c r="D72" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E72" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F72" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B73" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C73" t="s">
-        <v>235</v>
+        <v>508</v>
       </c>
       <c r="D73" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E73" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F73" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B74" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C74" t="s">
-        <v>530</v>
+        <v>187</v>
       </c>
       <c r="D74" t="s">
         <v>188</v>
       </c>
       <c r="E74" t="s">
-        <v>531</v>
+        <v>225</v>
       </c>
       <c r="F74" t="s">
-        <v>532</v>
+        <v>201</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>533</v>
@@ -4716,278 +5079,899 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B75" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="C75" t="s">
-        <v>534</v>
+        <v>181</v>
       </c>
       <c r="D75" t="s">
         <v>188</v>
       </c>
       <c r="E75" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="F75" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="B76" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="C76" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D76" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E76" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="F76" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="B77" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="C77" t="s">
-        <v>181</v>
+        <v>324</v>
       </c>
       <c r="D77" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="E77" t="s">
-        <v>540</v>
+        <v>281</v>
       </c>
       <c r="F77" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B78" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C78" t="s">
-        <v>181</v>
+        <v>324</v>
       </c>
       <c r="D78" t="s">
         <v>188</v>
       </c>
       <c r="E78" t="s">
-        <v>545</v>
+        <v>281</v>
       </c>
       <c r="F78" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B79" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C79" t="s">
-        <v>174</v>
+        <v>553</v>
       </c>
       <c r="D79" t="s">
         <v>188</v>
       </c>
       <c r="E79" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F79" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B80" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C80" t="s">
-        <v>536</v>
+        <v>324</v>
       </c>
       <c r="D80" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E80" t="s">
-        <v>555</v>
+        <v>452</v>
       </c>
       <c r="F80" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B81" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="C81" t="s">
-        <v>174</v>
+        <v>563</v>
       </c>
       <c r="D81" t="s">
         <v>188</v>
       </c>
       <c r="E81" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="F81" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B82" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="C82" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D82" t="s">
-        <v>399</v>
+        <v>188</v>
       </c>
       <c r="E82" t="s">
-        <v>562</v>
+        <v>401</v>
       </c>
       <c r="F82" t="s">
-        <v>563</v>
+        <v>266</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B83" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C83" t="s">
-        <v>235</v>
+        <v>572</v>
       </c>
       <c r="D83" t="s">
         <v>188</v>
       </c>
       <c r="E83" t="s">
-        <v>567</v>
+        <v>201</v>
       </c>
       <c r="F83" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B84" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C84" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D84" t="s">
         <v>188</v>
       </c>
       <c r="E84" t="s">
-        <v>276</v>
+        <v>578</v>
       </c>
       <c r="F84" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B85" t="s">
-        <v>576</v>
+        <v>269</v>
       </c>
       <c r="C85" t="s">
-        <v>577</v>
+        <v>270</v>
       </c>
       <c r="D85" t="s">
         <v>188</v>
       </c>
       <c r="E85" t="s">
-        <v>578</v>
+        <v>271</v>
       </c>
       <c r="F85" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B86" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C86" t="s">
-        <v>582</v>
+        <v>187</v>
       </c>
       <c r="D86" t="s">
-        <v>188</v>
+        <v>451</v>
       </c>
       <c r="E86" t="s">
+        <v>585</v>
+      </c>
+      <c r="F86" t="s">
+        <v>586</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>588</v>
+      </c>
+      <c r="B87" t="s">
+        <v>589</v>
+      </c>
+      <c r="C87" t="s">
+        <v>187</v>
+      </c>
+      <c r="D87" t="s">
+        <v>175</v>
+      </c>
+      <c r="E87" t="s">
+        <v>590</v>
+      </c>
+      <c r="F87" t="s">
         <v>201</v>
       </c>
-      <c r="F86" t="s">
-        <v>583</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>584</v>
+      <c r="H87" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>592</v>
+      </c>
+      <c r="B88" t="s">
+        <v>240</v>
+      </c>
+      <c r="C88" t="s">
+        <v>187</v>
+      </c>
+      <c r="D88" t="s">
+        <v>188</v>
+      </c>
+      <c r="E88" t="s">
+        <v>593</v>
+      </c>
+      <c r="F88" t="s">
+        <v>368</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>595</v>
+      </c>
+      <c r="B89" t="s">
+        <v>596</v>
+      </c>
+      <c r="C89" t="s">
+        <v>412</v>
+      </c>
+      <c r="D89" t="s">
+        <v>188</v>
+      </c>
+      <c r="E89" t="s">
+        <v>200</v>
+      </c>
+      <c r="F89" t="s">
+        <v>597</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>599</v>
+      </c>
+      <c r="B90" t="s">
+        <v>600</v>
+      </c>
+      <c r="C90" t="s">
+        <v>181</v>
+      </c>
+      <c r="D90" t="s">
+        <v>188</v>
+      </c>
+      <c r="E90" t="s">
+        <v>601</v>
+      </c>
+      <c r="F90" t="s">
+        <v>602</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>604</v>
+      </c>
+      <c r="B91" t="s">
+        <v>311</v>
+      </c>
+      <c r="C91" t="s">
+        <v>312</v>
+      </c>
+      <c r="D91" t="s">
+        <v>188</v>
+      </c>
+      <c r="E91" t="s">
+        <v>605</v>
+      </c>
+      <c r="F91" t="s">
+        <v>606</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>608</v>
+      </c>
+      <c r="B92" t="s">
+        <v>609</v>
+      </c>
+      <c r="C92" t="s">
+        <v>610</v>
+      </c>
+      <c r="D92" t="s">
+        <v>188</v>
+      </c>
+      <c r="E92" t="s">
+        <v>261</v>
+      </c>
+      <c r="F92" t="s">
+        <v>611</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>613</v>
+      </c>
+      <c r="B93" t="s">
+        <v>614</v>
+      </c>
+      <c r="C93" t="s">
+        <v>615</v>
+      </c>
+      <c r="D93" t="s">
+        <v>188</v>
+      </c>
+      <c r="E93" t="s">
+        <v>616</v>
+      </c>
+      <c r="F93" t="s">
+        <v>537</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>618</v>
+      </c>
+      <c r="B94" t="s">
+        <v>619</v>
+      </c>
+      <c r="C94" t="s">
+        <v>187</v>
+      </c>
+      <c r="D94" t="s">
+        <v>188</v>
+      </c>
+      <c r="E94" t="s">
+        <v>620</v>
+      </c>
+      <c r="F94" t="s">
+        <v>621</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>623</v>
+      </c>
+      <c r="B95" t="s">
+        <v>624</v>
+      </c>
+      <c r="C95" t="s">
+        <v>187</v>
+      </c>
+      <c r="D95" t="s">
+        <v>188</v>
+      </c>
+      <c r="E95" t="s">
+        <v>333</v>
+      </c>
+      <c r="F95" t="s">
+        <v>201</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>626</v>
+      </c>
+      <c r="B96" t="s">
+        <v>627</v>
+      </c>
+      <c r="C96" t="s">
+        <v>224</v>
+      </c>
+      <c r="D96" t="s">
+        <v>188</v>
+      </c>
+      <c r="E96" t="s">
+        <v>628</v>
+      </c>
+      <c r="F96" t="s">
+        <v>629</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>631</v>
+      </c>
+      <c r="B97" t="s">
+        <v>632</v>
+      </c>
+      <c r="C97" t="s">
+        <v>633</v>
+      </c>
+      <c r="D97" t="s">
+        <v>188</v>
+      </c>
+      <c r="E97" t="s">
+        <v>634</v>
+      </c>
+      <c r="F97" t="s">
+        <v>555</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>631</v>
+      </c>
+      <c r="B98" t="s">
+        <v>632</v>
+      </c>
+      <c r="C98" t="s">
+        <v>636</v>
+      </c>
+      <c r="D98" t="s">
+        <v>188</v>
+      </c>
+      <c r="E98" t="s">
+        <v>634</v>
+      </c>
+      <c r="F98" t="s">
+        <v>555</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>631</v>
+      </c>
+      <c r="B99" t="s">
+        <v>632</v>
+      </c>
+      <c r="C99" t="s">
+        <v>638</v>
+      </c>
+      <c r="D99" t="s">
+        <v>188</v>
+      </c>
+      <c r="E99" t="s">
+        <v>634</v>
+      </c>
+      <c r="F99" t="s">
+        <v>555</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>640</v>
+      </c>
+      <c r="B100" t="s">
+        <v>641</v>
+      </c>
+      <c r="C100" t="s">
+        <v>642</v>
+      </c>
+      <c r="D100" t="s">
+        <v>188</v>
+      </c>
+      <c r="E100" t="s">
+        <v>225</v>
+      </c>
+      <c r="F100" t="s">
+        <v>643</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>645</v>
+      </c>
+      <c r="B101" t="s">
+        <v>646</v>
+      </c>
+      <c r="C101" t="s">
+        <v>181</v>
+      </c>
+      <c r="D101" t="s">
+        <v>175</v>
+      </c>
+      <c r="E101" t="s">
+        <v>647</v>
+      </c>
+      <c r="F101" t="s">
+        <v>648</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>650</v>
+      </c>
+      <c r="B102" t="s">
+        <v>651</v>
+      </c>
+      <c r="C102" t="s">
+        <v>187</v>
+      </c>
+      <c r="D102" t="s">
+        <v>188</v>
+      </c>
+      <c r="E102" t="s">
+        <v>652</v>
+      </c>
+      <c r="F102" t="s">
+        <v>653</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>655</v>
+      </c>
+      <c r="B103" t="s">
+        <v>656</v>
+      </c>
+      <c r="C103" t="s">
+        <v>224</v>
+      </c>
+      <c r="D103" t="s">
+        <v>188</v>
+      </c>
+      <c r="E103" t="s">
+        <v>657</v>
+      </c>
+      <c r="F103" t="s">
+        <v>658</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>660</v>
+      </c>
+      <c r="B104" t="s">
+        <v>661</v>
+      </c>
+      <c r="C104" t="s">
+        <v>181</v>
+      </c>
+      <c r="D104" t="s">
+        <v>188</v>
+      </c>
+      <c r="E104" t="s">
+        <v>662</v>
+      </c>
+      <c r="F104" t="s">
+        <v>663</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>665</v>
+      </c>
+      <c r="B105" t="s">
+        <v>666</v>
+      </c>
+      <c r="C105" t="s">
+        <v>174</v>
+      </c>
+      <c r="D105" t="s">
+        <v>188</v>
+      </c>
+      <c r="E105" t="s">
+        <v>667</v>
+      </c>
+      <c r="F105" t="s">
+        <v>668</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>670</v>
+      </c>
+      <c r="B106" t="s">
+        <v>671</v>
+      </c>
+      <c r="C106" t="s">
+        <v>638</v>
+      </c>
+      <c r="D106" t="s">
+        <v>188</v>
+      </c>
+      <c r="E106" t="s">
+        <v>672</v>
+      </c>
+      <c r="F106" t="s">
+        <v>673</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>675</v>
+      </c>
+      <c r="B107" t="s">
+        <v>666</v>
+      </c>
+      <c r="C107" t="s">
+        <v>174</v>
+      </c>
+      <c r="D107" t="s">
+        <v>188</v>
+      </c>
+      <c r="E107" t="s">
+        <v>667</v>
+      </c>
+      <c r="F107" t="s">
+        <v>668</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>677</v>
+      </c>
+      <c r="B108" t="s">
+        <v>678</v>
+      </c>
+      <c r="C108" t="s">
+        <v>187</v>
+      </c>
+      <c r="D108" t="s">
+        <v>451</v>
+      </c>
+      <c r="E108" t="s">
+        <v>679</v>
+      </c>
+      <c r="F108" t="s">
+        <v>680</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>682</v>
+      </c>
+      <c r="B109" t="s">
+        <v>683</v>
+      </c>
+      <c r="C109" t="s">
+        <v>224</v>
+      </c>
+      <c r="D109" t="s">
+        <v>188</v>
+      </c>
+      <c r="E109" t="s">
+        <v>684</v>
+      </c>
+      <c r="F109" t="s">
+        <v>493</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>686</v>
+      </c>
+      <c r="B110" t="s">
+        <v>687</v>
+      </c>
+      <c r="C110" t="s">
+        <v>688</v>
+      </c>
+      <c r="D110" t="s">
+        <v>451</v>
+      </c>
+      <c r="E110" t="s">
+        <v>689</v>
+      </c>
+      <c r="F110" t="s">
+        <v>504</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>691</v>
+      </c>
+      <c r="B111" t="s">
+        <v>692</v>
+      </c>
+      <c r="C111" t="s">
+        <v>693</v>
+      </c>
+      <c r="D111" t="s">
+        <v>188</v>
+      </c>
+      <c r="E111" t="s">
+        <v>292</v>
+      </c>
+      <c r="F111" t="s">
+        <v>694</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>696</v>
+      </c>
+      <c r="B112" t="s">
+        <v>697</v>
+      </c>
+      <c r="C112" t="s">
+        <v>698</v>
+      </c>
+      <c r="D112" t="s">
+        <v>188</v>
+      </c>
+      <c r="E112" t="s">
+        <v>699</v>
+      </c>
+      <c r="F112" t="s">
+        <v>344</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>701</v>
+      </c>
+      <c r="B113" t="s">
+        <v>702</v>
+      </c>
+      <c r="C113" t="s">
+        <v>703</v>
+      </c>
+      <c r="D113" t="s">
+        <v>188</v>
+      </c>
+      <c r="E113" t="s">
+        <v>201</v>
+      </c>
+      <c r="F113" t="s">
+        <v>704</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>705</v>
       </c>
     </row>
   </sheetData>
@@ -5078,6 +6062,33 @@
     <hyperlink ref="H84" r:id="rId83"/>
     <hyperlink ref="H85" r:id="rId84"/>
     <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
